--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>מיתריי – שיהא בי את האומץ</v>
       </c>
       <c r="B2" t="str">
-        <v>7 days ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%aa%d7%a8%d7%99%d7%99-%d7%a9%d7%99%d7%94%d7%90-%d7%91%d7%99-%d7%90%d7%aa-%d7%94%d7%90%d7%95%d7%9e%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 days ago</v>
+        <v>"שיהא בי את האומץ” של מיתריי (מאיה ביתנר) הוא שיר שממוקם בין תפילה אישית לבין טקס קולקטיבי. זה לא רק שיר במובן הפופולרי אלא חוויה כמעט מדיטטיבית־שבטית, שמבקשת לפרק פחדים ולהזמין חופש. ליבת  השיר נמצאת במשפט החוזר: "שיהא בי את</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Danna</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>מיתריי – שיהא בי את האומץ</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B3" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-29</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B4" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-29</v>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-29</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B6" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-29</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Beck</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-29</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B9" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-29</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Digster Pop Music</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-29</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Beck</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-29</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>The All-American Rejects</v>
+        <v>Beck</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Armin van Buuren</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B13" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-29</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-29</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Madonna</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Freya Ridings</v>
+        <v>Madonna</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-29</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Celine Dion</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B17" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-29</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Peter Gabriel</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B18" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-29</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B19" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-29</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B20" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-29</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>ERNEST</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>ERNEST</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B23" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dean Lewis</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Kip Moore</v>
+        <v>Bella White</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Ben Gallaher</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B28" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Johnny Orlando</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Tyla</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B31" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-29</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Tyla</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-29</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lana Del Rey</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-29</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Loreen</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-29</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Loreen</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-29</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Tenille Townes</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B36" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-29</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Danna</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B38" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-29</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>OneRepublic</v>
+        <v>Danna</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B39" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-29</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The Revivalists</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-29</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>James Smith</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B41" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-29</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Holly Humberstone</v>
+        <v>James Smith</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B42" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-29</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-29</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-29</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Conan Gray</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B47" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-29</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>TemplesOfficial</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-29</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Laufey</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-29</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>bleachers</v>
+        <v>Laufey</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-29</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-29</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>LANY</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-29</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>LANY</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-29</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-29</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-29</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Kygo and carter faith</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-29</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>florencemachine</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-29</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Scorpions</v>
+        <v>florencemachine</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-29</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-29</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-29</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-29</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-29</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Mae Muller</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-29</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dead Pony</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-29</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-29</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-29</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>kenzie</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-29</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>kenzie</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-29</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Laufey</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-29</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>Laufey</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-29</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Mei Semones</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-29</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Evanescence</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-29</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>elijah woods</v>
+        <v>Evanescence</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-29</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>colby!</v>
+        <v>elijah woods</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-29</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Chainsmokers</v>
+        <v>colby!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-29</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>aron!</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-29</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Owen Riegling</v>
+        <v>aron!</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-29</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-29</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Teddy Swims</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-29</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-29</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-29</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-29</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-29</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Freya Skye</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-29</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Adams</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-29</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>We Three</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-29</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Dermot Kennedy</v>
+        <v>We Three</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Bebe Rexha</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-29</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-29</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>METTE</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-29</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Saint Harison</v>
+        <v>METTE</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-29</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>NewDad</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-29</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Danna</v>
+        <v>NewDad</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-29</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>florencemachine</v>
+        <v>Danna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-29</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>HYBE LABELS</v>
+        <v>florencemachine</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-29</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kungs</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Charlie Puth</v>
+        <v>Kungs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Madison Cunningham</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>IT'S OK</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>IT'S OK - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:19</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Bryson Tiller</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kehlani</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:06</v>
+        <v>2:19</v>
       </c>
       <c r="H103" t="str">
-        <v>Kehlani</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L103" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Después de ti</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Después de ti - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G104" t="str">
-        <v>4:35</v>
+        <v>3:06</v>
       </c>
       <c r="H104" t="str">
-        <v>KAROL G</v>
+        <v>Kehlani</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L104" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dando Vueltas</v>
+        <v>Después de ti</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:12</v>
+        <v>4:35</v>
       </c>
       <c r="H105" t="str">
-        <v>Rauw Alejandro</v>
+        <v>KAROL G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L105" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Doors</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:51</v>
+        <v>3:12</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L106" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Doors</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G107" t="str">
-        <v>3:48</v>
+        <v>3:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Langley</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L107" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Todos nos Shipean</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H108" t="str">
-        <v>Fuerza Regida</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L108" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Ojitos Bellos</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:59</v>
+        <v>2:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Grupo Frontera</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L109" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>REDRED</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>2:59</v>
       </c>
       <c r="H110" t="str">
-        <v>CORTIS</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L110" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Little More Time</v>
+        <v>REDRED</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dinner Party</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G111" t="str">
-        <v>3:38</v>
+        <v>2:43</v>
       </c>
       <c r="H111" t="str">
-        <v>Niall Horan</v>
+        <v>CORTIS</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L111" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Cool Buzz</v>
+        <v>Little More Time</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G112" t="str">
-        <v>2:32</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>Violet Grohl</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L112" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>earth is turning</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>2:32</v>
       </c>
       <c r="H113" t="str">
-        <v>horsegiirL</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L113" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Better</v>
+        <v>earth is turning</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>U</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G114" t="str">
-        <v>3:50</v>
+        <v>4:49</v>
       </c>
       <c r="H114" t="str">
-        <v>Baauer</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L114" t="str">
-        <v>Better - Baauer</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G115" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H115" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L115" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H116" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L116" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H117" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L117" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G118" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H118" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L118" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H119" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L119" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G121" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L121" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H122" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L122" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H123" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L123" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L124" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G125" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H125" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L125" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G126" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L126" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H127" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L127" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G128" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L128" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L129" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G130" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L130" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H131" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L131" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G132" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H132" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L132" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H133" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L133" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H134" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L134" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G135" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H135" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L135" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H136" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L136" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H137" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L137" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L138" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H139" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L139" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H140" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L140" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H141" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L141" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G142" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H142" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L142" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G143" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H143" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L143" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G144" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H144" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L144" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L145" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G146" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L146" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H147" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L147" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H148" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L148" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G149" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H149" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L149" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L150" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L151" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H152" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L152" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Leave Me For Good</v>
+        <v>oh child</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:58</v>
+        <v>2:02</v>
       </c>
       <c r="H153" t="str">
-        <v>tbh</v>
+        <v>kai devega</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L153" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Dance To This</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Ritual</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H154" t="str">
-        <v>Icona Pop</v>
+        <v>tbh</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L154" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H155" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L156" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H157" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L157" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H158" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L158" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G159" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L159" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H160" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L160" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H161" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L161" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H162" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L162" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G163" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L163" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G164" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H164" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L164" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G165" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L165" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H166" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L166" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H167" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L167" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L168" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H169" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L169" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G170" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L170" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G171" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L171" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H172" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L172" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H173" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L173" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G174" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H174" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L174" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H175" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L175" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H176" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L176" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L177" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>No Invite</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>The Last Balloon</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G178" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Lane 8</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L178" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Bando</v>
+        <v>No Invite</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HOPE!!</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G179" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L179" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Bando</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G180" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>Duke Dumont</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L180" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Physical</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Physical - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H181" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L181" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H182" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L182" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L183" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H184" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L184" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L185" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H186" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L186" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G187" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H187" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L187" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L188" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G189" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L189" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G190" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L190" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G191" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L191" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L192" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H193" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L193" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L194" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H195" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L195" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G196" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H196" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L196" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G197" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H197" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L197" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G198" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H198" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L198" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-29</v>
@@ -7937,68 +7937,106 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G199" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H199" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L199" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D201" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G201" t="str">
         <v>4:34</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H201" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L201" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%aa%d7%a8%d7%99%d7%99-%d7%a9%d7%99%d7%94%d7%90-%d7%91%d7%99-%d7%90%d7%aa-%d7%94%d7%90%d7%95%d7%9e%d7%a5/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שיהא בי את האומץ” של מיתריי (מאיה ביתנר) הוא שיר שממוקם בין תפילה אישית לבין טקס קולקטיבי. זה לא רק שיר במובן הפופולרי אלא חוויה כמעט מדיטטיבית־שבטית, שמבקשת לפרק פחדים ולהזמין חופש. ליבת  השיר נמצאת במשפט החוזר: "שיהא בי את</v>
+        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
     </row>
     <row r="3">
@@ -933,7 +933,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B18" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B19" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B20" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
+        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
     </row>
     <row r="3">
@@ -1921,7 +1921,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G42" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-29</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>7 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-29</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Armik</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Europe</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Cannons</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Beck</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Muse</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Digster Pop Music</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Beck</v>
+        <v>Scorpions</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>The All-American Rejects</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Armin van Buuren</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Demi Lovato</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Madonna</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Freya Ridings</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Celine Dion</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Peter Gabriel</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>ERNEST</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Bella White</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Kip Moore</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Ben Gallaher</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Johnny Orlando</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tyla</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lana Del Rey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Loreen</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Tenille Townes</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Danna</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>OneRepublic</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>The Revivalists</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>James Smith</v>
+        <v>Danna</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Holly Humberstone</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Ava Max</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>John Summit</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Ava Max</v>
+        <v>Beck</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Conan Gray</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>TemplesOfficial</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Laufey</v>
+        <v>Beck</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>bleachers</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>LANY</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Madonna</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>florencemachine</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Scorpions</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>HAUSER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Holly Humberstone</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-29</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Mae Muller</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-29</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dead Pony</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-29</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-29</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>kenzie</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Foo Fighters</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Laufey</v>
+        <v>Tyla</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mei Semones</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Evanescence</v>
+        <v>Loreen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>elijah woods</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>colby!</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Chainsmokers</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>aron!</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-29</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Owen Riegling</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-29</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-29</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Teddy Swims</v>
+        <v>James Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-29</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-29</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Ava Max</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-29</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Sunday (1994)</v>
+        <v>John Summit</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-29</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Ava Max</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-29</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Freya Skye</v>
+        <v>Danna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-29</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Bryan Adams</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-29</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>We Three</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-29</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Bebe Rexha</v>
+        <v>bleachers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-29</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>METTE</v>
+        <v>LANY</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Saint Harison</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>NewDad</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Danna</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>florencemachine</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-29</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>HYBE LABELS</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-29</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Kungs</v>
+        <v>Scorpions</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-29</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Charlie Puth</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-29</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nothing But Thieves</v>
+        <v>HAUSER</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-29</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-29</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Madison Cunningham</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-29</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Armin van Buuren</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Lioness</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H102" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L102" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>IT'S OK</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G103" t="str">
-        <v>2:19</v>
+        <v>3:06</v>
       </c>
       <c r="H103" t="str">
-        <v>Bryson Tiller</v>
+        <v>Kehlani</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L103" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Después de ti</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Kehlani</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:06</v>
+        <v>4:35</v>
       </c>
       <c r="H104" t="str">
-        <v>Kehlani</v>
+        <v>KAROL G</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L104" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Después de ti</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Después de ti - Single</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:35</v>
+        <v>3:12</v>
       </c>
       <c r="H105" t="str">
-        <v>KAROL G</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L105" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Dando Vueltas</v>
+        <v>Doors</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v>3:12</v>
+        <v>3:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Rauw Alejandro</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Doors</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Great Divide</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:51</v>
+        <v>3:48</v>
       </c>
       <c r="H107" t="str">
-        <v>Noah Kahan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L107" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:48</v>
+        <v>2:16</v>
       </c>
       <c r="H108" t="str">
-        <v>Ella Langley</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L108" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Todos nos Shipean</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:16</v>
+        <v>2:59</v>
       </c>
       <c r="H109" t="str">
-        <v>Fuerza Regida</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L109" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ojitos Bellos</v>
+        <v>REDRED</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G110" t="str">
-        <v>2:59</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Grupo Frontera</v>
+        <v>CORTIS</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L110" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>REDRED</v>
+        <v>Little More Time</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G111" t="str">
-        <v>2:43</v>
+        <v>3:38</v>
       </c>
       <c r="H111" t="str">
-        <v>CORTIS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L111" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Little More Time</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Dinner Party</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H112" t="str">
-        <v>Niall Horan</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L112" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Cool Buzz</v>
+        <v>earth is turning</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Be Sweet To Me</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G113" t="str">
-        <v>2:32</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Violet Grohl</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L113" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>earth is turning</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-29</v>
@@ -4707,25 +4707,25 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G114" t="str">
-        <v>4:49</v>
+        <v>2:32</v>
       </c>
       <c r="H114" t="str">
-        <v>horsegiirL</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L114" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="115">

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>פרחי ירושלים - האור שלא יכבה</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410653&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Keith Urban</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>פרחי ירושלים - האור שלא יכבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>אופיר חדד- ילדות העיר שלי</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410652&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>אופיר חדד- ילדות העיר שלי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>שלומי ימין - רוצה להיות שלך</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410651&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Armik</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>שלומי ימין - רוצה להיות שלך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410650&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>רותם שפי - רילוקיישן</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410649&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>רותם שפי - רילוקיישן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>פרידה - ילדה מבורכת</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410648&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>פרידה - ילדה מבורכת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>נתי בן שלום - שוב יכול</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410647&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Muse</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>נתי בן שלום - שוב יכול</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410646&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-29</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>אלעד אביבי - ימנו זלקה</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-29</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410645&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-29</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Shaboozey</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>אלעד אביבי - ימנו זלקה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Scorpions</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Meghan Trainor</v>
+        <v>Danna</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Armik</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Europe</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Icona Pop</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Jackson</v>
+        <v>Muse</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>The All-American Rejects</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-29</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Ringo Starr</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-29</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Scorpions</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-29</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-29</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-29</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-29</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-29</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-29</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lukas Graham</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-29</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-29</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-29</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Haiden Henderson</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-29</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-29</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Foo Fighters</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-29</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-29</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bublé</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-29</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Malcolm Todd</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-29</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Sam Feldt</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>RUEL</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Duran Duran</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danna</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Beck</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Digster Pop Music</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Beck</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The All-American Rejects</v>
+        <v>Danna</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madonna</v>
+        <v>Cannons</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Freya Ridings</v>
+        <v>Beck</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Celine Dion</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Peter Gabriel</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Beck</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Kid LAROI.</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>ERNEST</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dean Lewis</v>
+        <v>Madonna</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-29</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B64" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-29</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B65" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-29</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B66" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-29</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Ben Gallaher</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B67" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-29</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-29</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-29</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Tyla</v>
+        <v>ERNEST</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B70" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-29</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Lewis Capaldi</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lana Del Rey</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Loreen</v>
+        <v>Bella White</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tenille Townes</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-29</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-29</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Revivalists</v>
+        <v>Tyla</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>James Smith</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-29</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ava Max</v>
+        <v>Loreen</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-29</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>John Summit</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-29</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ava Max</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-29</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Danna</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-29</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Conan Gray</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-29</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>TemplesOfficial</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-29</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>bleachers</v>
+        <v>James Smith</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-29</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-29</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>LANY</v>
+        <v>Ava Max</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-29</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>John Summit</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-29</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Ava Max</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-29</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Danna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-29</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-29</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>florencemachine</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Scorpions</v>
+        <v>Laufey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>bleachers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>HAUSER</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>LANY</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Mae Muller</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lioness</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Maya Hawke</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kehlani</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Kehlani</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Después de ti</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Después de ti - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>4:35</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>KAROL G</v>
+        <v>florencemachine</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dando Vueltas</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:12</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Rauw Alejandro</v>
+        <v>Scorpions</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Doors</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:51</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Ella Langley</v>
+        <v>HAUSER</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Todos nos Shipean</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:16</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Fuerza Regida</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Ojitos Bellos</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:59</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Grupo Frontera</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>REDRED</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>CORTIS</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Little More Time</v>
+        <v>Lioness</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dinner Party</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G111" t="str">
-        <v>3:38</v>
+        <v>3:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Niall Horan</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L111" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>IT'S OK</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G112" t="str">
-        <v>2:19</v>
+        <v>3:06</v>
       </c>
       <c r="H112" t="str">
-        <v>Bryson Tiller</v>
+        <v>Kehlani</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L112" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>earth is turning</v>
+        <v>Después de ti</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>4:35</v>
       </c>
       <c r="H113" t="str">
-        <v>horsegiirL</v>
+        <v>KAROL G</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L113" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cool Buzz</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>Violet Grohl</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L114" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Better</v>
+        <v>Doors</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>U</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G115" t="str">
-        <v>3:50</v>
+        <v>3:51</v>
       </c>
       <c r="H115" t="str">
-        <v>Baauer</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L115" t="str">
-        <v>Better - Baauer</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ride Lonesome</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:32</v>
+        <v>3:48</v>
       </c>
       <c r="H116" t="str">
-        <v>Beck</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L116" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>1:56</v>
+        <v>2:16</v>
       </c>
       <c r="H117" t="str">
-        <v>Billie Eilish</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Big Mama</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H118" t="str">
-        <v>Latto</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L118" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Born To Die</v>
+        <v>REDRED</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Born To Die - Single</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G119" t="str">
-        <v>2:45</v>
+        <v>2:43</v>
       </c>
       <c r="H119" t="str">
-        <v>Shaboozey</v>
+        <v>CORTIS</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L119" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Little More Time</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>3:38</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L120" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Tiny Raisin</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Loveland</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>2:19</v>
       </c>
       <c r="H121" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L121" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Fantasy</v>
+        <v>earth is turning</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G122" t="str">
-        <v>2:21</v>
+        <v>4:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Demi Lovato</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L122" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Already Know</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G123" t="str">
-        <v>2:37</v>
+        <v>2:32</v>
       </c>
       <c r="H123" t="str">
-        <v>The Chainsmokers</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L123" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PIECES</v>
+        <v>Better</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>U</v>
       </c>
       <c r="G124" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H124" t="str">
-        <v>The Kid LAROI</v>
+        <v>Baauer</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L124" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shimmer</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Toy With Me</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:47</v>
+        <v>4:32</v>
       </c>
       <c r="H125" t="str">
-        <v>Meghan Trainor</v>
+        <v>Beck</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L125" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Window</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Your Favorite Toy</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>1:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Foo Fighters</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L126" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Reward the Scars</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G127" t="str">
-        <v>3:35</v>
+        <v>2:29</v>
       </c>
       <c r="H127" t="str">
-        <v>Korn</v>
+        <v>Latto</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L127" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Songs About Us</v>
+        <v>Born To Die</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Songs About Us</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>2:45</v>
       </c>
       <c r="H128" t="str">
-        <v>Jason Aldean</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L128" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>La Buena</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>La Buena - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G129" t="str">
-        <v>2:16</v>
+        <v>3:08</v>
       </c>
       <c r="H129" t="str">
-        <v>Carín León</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L129" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>You Better Know</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>Loveland</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H130" t="str">
-        <v>Ebony Riley</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L130" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Planting Tomatoes</v>
+        <v>Fantasy</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:35</v>
+        <v>2:21</v>
       </c>
       <c r="H131" t="str">
-        <v>Lucy Dacus</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L131" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Back of a Truck</v>
+        <v>Already Know</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>American Stories</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>4:00</v>
+        <v>2:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Rostam</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L132" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FIX UR FACE</v>
+        <v>PIECES</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H133" t="str">
-        <v>mgk</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L133" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>CELEBRATION</v>
+        <v>Shimmer</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G134" t="str">
-        <v>2:33</v>
+        <v>2:47</v>
       </c>
       <c r="H134" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L134" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Door</v>
+        <v>Window</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G135" t="str">
-        <v>3:54</v>
+        <v>3:37</v>
       </c>
       <c r="H135" t="str">
-        <v>Conan Gray</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L135" t="str">
-        <v>Door - Conan Gray</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hate Myself</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:32</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Ruel</v>
+        <v>Korn</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L136" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>DREAMBOY</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G137" t="str">
-        <v>3:17</v>
+        <v>2:52</v>
       </c>
       <c r="H137" t="str">
-        <v>MICO</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L137" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>La Buena</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H138" t="str">
-        <v>Daniel Seavey</v>
+        <v>Carín León</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L138" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>You Better Know</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G139" t="str">
-        <v>3:23</v>
+        <v>3:13</v>
       </c>
       <c r="H139" t="str">
-        <v>The Two Lips</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>car crash</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>car crash - Single</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:40</v>
+        <v>3:35</v>
       </c>
       <c r="H140" t="str">
-        <v>jigitz</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L140" t="str">
-        <v>car crash - jigitz</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>All This Disaster</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>All This Disaster - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G141" t="str">
-        <v>3:22</v>
+        <v>4:00</v>
       </c>
       <c r="H141" t="str">
-        <v>Sarah McLachlan</v>
+        <v>Rostam</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L141" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Better Days</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:35</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>mgk</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L142" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Rising Skyline</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Location Lost</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:32</v>
+        <v>2:33</v>
       </c>
       <c r="H143" t="str">
-        <v>Failure</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L143" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Cryogen</v>
+        <v>Door</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Wow! Signal</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G144" t="str">
-        <v>5:01</v>
+        <v>3:54</v>
       </c>
       <c r="H144" t="str">
-        <v>Muse</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L144" t="str">
-        <v>Cryogen - Muse</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:21</v>
+        <v>2:32</v>
       </c>
       <c r="H145" t="str">
-        <v>Nick Cave</v>
+        <v>Ruel</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L145" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:39</v>
+        <v>3:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Genesis Owusu</v>
+        <v>MICO</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L146" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>HBO</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>HBO - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:42</v>
+        <v>2:52</v>
       </c>
       <c r="H147" t="str">
-        <v>Yung Gravy</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L147" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Need For Speed</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Need For Speed - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:15</v>
+        <v>3:23</v>
       </c>
       <c r="H148" t="str">
-        <v>Kim Petras</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L148" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>collide</v>
+        <v>car crash</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>girls like girls (the album)</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:43</v>
+        <v>2:40</v>
       </c>
       <c r="H149" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>jigitz</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L149" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>freak for you</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>freak for you - Single</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:26</v>
+        <v>3:22</v>
       </c>
       <c r="H150" t="str">
-        <v>Haiden Henderson</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L150" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Anymore</v>
+        <v>Better Days</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>3:35</v>
       </c>
       <c r="H151" t="str">
-        <v>Asha Banks</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L151" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Why Am I Here</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Location Lost</v>
       </c>
       <c r="G152" t="str">
-        <v>3:17</v>
+        <v>4:32</v>
       </c>
       <c r="H152" t="str">
-        <v>Presley Regier</v>
+        <v>Failure</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L152" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>oh child</v>
+        <v>Cryogen</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>oh child - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G153" t="str">
-        <v>2:02</v>
+        <v>5:01</v>
       </c>
       <c r="H153" t="str">
-        <v>kai devega</v>
+        <v>Muse</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L153" t="str">
-        <v>oh child - kai devega</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Leave Me For Good</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G154" t="str">
-        <v>2:58</v>
+        <v>1:21</v>
       </c>
       <c r="H154" t="str">
-        <v>tbh</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L154" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Dance To This</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G155" t="str">
-        <v>2:54</v>
+        <v>3:39</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L155" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>HBO</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:58</v>
+        <v>3:42</v>
       </c>
       <c r="H156" t="str">
-        <v>Tauren Wells</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L156" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You Can Have Him</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G157" t="str">
         <v>3:15</v>
       </c>
       <c r="H157" t="str">
-        <v>Carly Pearce</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L157" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Backwards</v>
+        <v>collide</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Backwards - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G158" t="str">
-        <v>3:17</v>
+        <v>3:43</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L158" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Love Ain't Shit</v>
+        <v>freak for you</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Serial Romantic</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:27</v>
+        <v>2:26</v>
       </c>
       <c r="H159" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L159" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Anymore</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:43</v>
+        <v>2:37</v>
       </c>
       <c r="H160" t="str">
-        <v>Isaiah Falls</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L160" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>3:42</v>
+        <v>3:17</v>
       </c>
       <c r="H161" t="str">
-        <v>PARTYOF2</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L161" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dance In The USA</v>
+        <v>oh child</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:59</v>
+        <v>2:02</v>
       </c>
       <c r="H162" t="str">
-        <v>Show Me the Body</v>
+        <v>kai devega</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L162" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Tremolo</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:43</v>
+        <v>2:58</v>
       </c>
       <c r="H163" t="str">
-        <v>Metric</v>
+        <v>tbh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L163" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>In the Dark</v>
+        <v>Dance To This</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>The End is Not the End</v>
+        <v>Ritual</v>
       </c>
       <c r="G164" t="str">
-        <v>3:52</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>Atreyu</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L164" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:36</v>
+        <v>3:58</v>
       </c>
       <c r="H165" t="str">
-        <v>Modest Mouse</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L165" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Saw Your Face</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:09</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L166" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Demons In Your Choir</v>
+        <v>Backwards</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Grateful</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:16</v>
+        <v>3:17</v>
       </c>
       <c r="H167" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L167" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Full Circle</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>3:27</v>
       </c>
       <c r="H168" t="str">
-        <v>Leonie Biney</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L168" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:39</v>
+        <v>3:43</v>
       </c>
       <c r="H169" t="str">
-        <v>Sophia Stel</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L169" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Destined For Greatness</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:03</v>
+        <v>3:42</v>
       </c>
       <c r="H170" t="str">
-        <v>Luh Tyler</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L170" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sadetra Son</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H171" t="str">
-        <v>Montana 700</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L171" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Tremolo</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G172" t="str">
-        <v>2:31</v>
+        <v>3:43</v>
       </c>
       <c r="H172" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Metric</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L172" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>In the Dark</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G173" t="str">
-        <v>3:28</v>
+        <v>3:52</v>
       </c>
       <c r="H173" t="str">
-        <v>Beach Bunny</v>
+        <v>Atreyu</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Twice</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G174" t="str">
-        <v>2:32</v>
+        <v>4:36</v>
       </c>
       <c r="H174" t="str">
-        <v>Arrows in Action</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L174" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Asleep Talking</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:36</v>
+        <v>3:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L175" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>hide and seek</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>hide and seek - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G176" t="str">
-        <v>2:47</v>
+        <v>4:16</v>
       </c>
       <c r="H176" t="str">
-        <v>Hailey Picardi</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L176" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Be the One</v>
+        <v>Full Circle</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Be the One - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Adam Port</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L177" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>World Is Mine</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>World Is Mine</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>3:39</v>
       </c>
       <c r="H178" t="str">
-        <v>Lane 8</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L178" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Invite</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>The Last Balloon</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G179" t="str">
-        <v>3:26</v>
+        <v>2:03</v>
       </c>
       <c r="H179" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L179" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bando</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HOPE!!</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>2:51</v>
       </c>
       <c r="H180" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Montana 700</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L180" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G181" t="str">
         <v>2:31</v>
       </c>
       <c r="H181" t="str">
-        <v>Duke Dumont</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Physical</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Physical - Single</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>3:28</v>
       </c>
       <c r="H182" t="str">
-        <v>J. Worra</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L182" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Twice</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G183" t="str">
-        <v>3:19</v>
+        <v>2:32</v>
       </c>
       <c r="H183" t="str">
-        <v>LEGADO 7</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>AM I OKAY?!</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:37</v>
+        <v>2:36</v>
       </c>
       <c r="H184" t="str">
-        <v>Durand Bernarr</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L184" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Have You Ever</v>
+        <v>hide and seek</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Have You Ever - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H185" t="str">
-        <v>FEYI</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L185" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Campeones</v>
+        <v>Be the One</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Campeones - Single</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H186" t="str">
-        <v>Cypress Hill</v>
+        <v>Adam Port</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L186" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G187" t="str">
-        <v>3:27</v>
+        <v>4:46</v>
       </c>
       <c r="H187" t="str">
-        <v>Mina Tindle</v>
+        <v>Lane 8</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L187" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>tennis practice</v>
+        <v>No Invite</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>exposure therapy - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G188" t="str">
-        <v>2:41</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Khatumu</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L188" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Moon Not Mine</v>
+        <v>Bando</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Singing</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>3:17</v>
       </c>
       <c r="H189" t="str">
-        <v>Gia Margaret</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L189" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>You Say I Love You</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>2:31</v>
       </c>
       <c r="H190" t="str">
-        <v>Quiet Light</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L190" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Physical</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>5:54</v>
+        <v>2:40</v>
       </c>
       <c r="H191" t="str">
-        <v>Friko</v>
+        <v>J. Worra</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L191" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>7:05</v>
+        <v>3:19</v>
       </c>
       <c r="H192" t="str">
-        <v>Zee Nxumalo</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L192" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Cake</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cake - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:36</v>
+        <v>3:37</v>
       </c>
       <c r="H193" t="str">
-        <v>Mila Smith</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L193" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>from a distance</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>from a distance - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H194" t="str">
-        <v>Luz</v>
+        <v>FEYI</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L194" t="str">
-        <v>from a distance - Luz</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Second Hand</v>
+        <v>Campeones</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Second Hand - Single</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:24</v>
+        <v>3:48</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L195" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mnikeni</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Ku Ngawe</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G196" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H196" t="str">
-        <v>Thando Zide</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L196" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lorcan's Song</v>
+        <v>tennis practice</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>2:40</v>
+        <v>2:41</v>
       </c>
       <c r="H197" t="str">
-        <v>Christian Henson</v>
+        <v>Khatumu</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L197" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>In Dark Distortion</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Singing</v>
       </c>
       <c r="G198" t="str">
-        <v>3:50</v>
+        <v>3:37</v>
       </c>
       <c r="H198" t="str">
-        <v>At The Gates</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L198" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>All Souls Rising</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G199" t="str">
-        <v>3:35</v>
+        <v>3:06</v>
       </c>
       <c r="H199" t="str">
-        <v>Sepultura</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L199" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Other Hells</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-29</v>
@@ -7975,68 +7975,410 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Other Hells - Single</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G200" t="str">
-        <v>2:06</v>
+        <v>5:54</v>
       </c>
       <c r="H200" t="str">
-        <v>Ceremony</v>
+        <v>Friko</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L200" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Guqa (My Prayer)</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Izinja Zam: Vol. I - EP</v>
+      </c>
+      <c r="G201" t="str">
+        <v>7:05</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Zee Nxumalo</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Cake</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Cake - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:36</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Mila Smith</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Cake - Mila Smith</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>from a distance</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>from a distance - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Luz</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+      </c>
+      <c r="L203" t="str">
+        <v>from a distance - Luz</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Second Hand</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Second Hand - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Anais Cardot</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Second Hand - Anais Cardot</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Mnikeni</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Ku Ngawe</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:08</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Thando Zide</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Mnikeni - Thando Zide</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Lorcan's Song</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:40</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Christian Henson</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Lorcan's Song - Christian Henson</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>In Dark Distortion</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:50</v>
+      </c>
+      <c r="H207" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+      </c>
+      <c r="L207" t="str">
+        <v>In Dark Distortion - At The Gates</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>All Souls Rising</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>The Cloud Of Unknowing - EP</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Sepultura</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+      </c>
+      <c r="L208" t="str">
+        <v>All Souls Rising - Sepultura</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D210" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G210" t="str">
         <v>4:34</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H210" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K210" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L210" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - האור שלא יכבה</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-29</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410653&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - האור שלא יכבה</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אופיר חדד- ילדות העיר שלי</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-29</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410652&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אופיר חדד- ילדות העיר שלי</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שלומי ימין - רוצה להיות שלך</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410651&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שלומי ימין - רוצה להיות שלך</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410650&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רותם שפי - רילוקיישן</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410649&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רותם שפי - רילוקיישן</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פרידה - ילדה מבורכת</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410648&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>פרידה - ילדה מבורכת</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נתי בן שלום - שוב יכול</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410647&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Muse</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נתי בן שלום - שוב יכול</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-29</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410646&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-29</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלעד אביבי - ימנו זלקה</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-29</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410645&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-29</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלעד אביבי - ימנו זלקה</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 hours ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 hours ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Keith Urban</v>
+        <v>Scorpions</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>21 hours ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>21 hours ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Danna</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Armik</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Europe</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Foo Fighters</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Muse</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-29</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Shaboozey</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-29</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Scorpions</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-29</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Meghan Trainor</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-29</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-29</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-29</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-29</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Icona Pop</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-29</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Michael Jackson</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-29</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The All-American Rejects</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-29</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Ringo Starr</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-29</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-29</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Demi Lovato</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-29</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Dean Lewis</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-29</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Matt Hansen</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-29</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ella Langley</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-29</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Meghan Trainor</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Lukas Graham</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>RUEL</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Haiden Henderson</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Conan Gray</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Foo Fighters</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Ringo Starr</v>
+        <v>Danna</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Michael Bublé</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Malcolm Todd</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Sam Feldt</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Niall Horan</v>
+        <v>Beck</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Duran Duran</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Freya Skye</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>OneRepublic</v>
+        <v>Beck</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Danna</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Cannons</v>
+        <v>Madonna</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Beck</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Digster Pop Music</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Beck</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The All-American Rejects</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Armin van Buuren</v>
+        <v>ERNEST</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Demi Lovato</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Madonna</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-29</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Freya Ridings</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-29</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Celine Dion</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-29</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Peter Gabriel</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-29</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-29</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Jessie Ware</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-29</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-29</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>ERNEST</v>
+        <v>Tyla</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-29</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Dean Lewis</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Bella White</v>
+        <v>Loreen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Kip Moore</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Ben Gallaher</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-29</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Johnny Orlando</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-29</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tyla</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Lewis Capaldi</v>
+        <v>James Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Lana Del Rey</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-29</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Loreen</v>
+        <v>Ava Max</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-29</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Bonnie Tyler</v>
+        <v>John Summit</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-29</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Tenille Townes</v>
+        <v>Ava Max</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-29</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Danna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-29</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-29</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>OneRepublic</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>The Revivalists</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-29</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>James Smith</v>
+        <v>bleachers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-29</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Holly Humberstone</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-29</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Ava Max</v>
+        <v>LANY</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-29</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>John Summit</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-29</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Ava Max</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-29</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Danna</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-29</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Conan Gray</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-29</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>TemplesOfficial</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Laufey</v>
+        <v>Scorpions</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>bleachers</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nothing But Thieves</v>
+        <v>HAUSER</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>LANY</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Lioness</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H102" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L102" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>Kehlani</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H103" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Kehlani</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L103" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Después de ti</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>4:35</v>
       </c>
       <c r="H104" t="str">
-        <v>florencemachine</v>
+        <v>KAROL G</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L104" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:12</v>
       </c>
       <c r="H105" t="str">
-        <v>Scorpions</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L105" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Doors</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Holly Humberstone</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H107" t="str">
-        <v>HAUSER</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L107" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H108" t="str">
-        <v>Holly Humberstone</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L108" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H109" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L109" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>REDRED</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Mae Muller</v>
+        <v>CORTIS</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L110" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lioness</v>
+        <v>Little More Time</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G111" t="str">
-        <v>3:32</v>
+        <v>3:38</v>
       </c>
       <c r="H111" t="str">
-        <v>Maya Hawke</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L111" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Kehlani</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:06</v>
+        <v>2:19</v>
       </c>
       <c r="H112" t="str">
-        <v>Kehlani</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L112" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Después de ti</v>
+        <v>earth is turning</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Después de ti - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G113" t="str">
-        <v>4:35</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>KAROL G</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L113" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Dando Vueltas</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>2:32</v>
       </c>
       <c r="H114" t="str">
-        <v>Rauw Alejandro</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L114" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Doors</v>
+        <v>Better</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>The Great Divide</v>
+        <v>U</v>
       </c>
       <c r="G115" t="str">
-        <v>3:51</v>
+        <v>3:50</v>
       </c>
       <c r="H115" t="str">
-        <v>Noah Kahan</v>
+        <v>Baauer</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L115" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:48</v>
+        <v>4:32</v>
       </c>
       <c r="H116" t="str">
-        <v>Ella Langley</v>
+        <v>Beck</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L116" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Todos nos Shipean</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:16</v>
+        <v>1:56</v>
       </c>
       <c r="H117" t="str">
-        <v>Fuerza Regida</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L117" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ojitos Bellos</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G118" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>Latto</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L118" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>REDRED</v>
+        <v>Born To Die</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:43</v>
+        <v>2:45</v>
       </c>
       <c r="H119" t="str">
-        <v>CORTIS</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L119" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Little More Time</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dinner Party</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>3:38</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>Niall Horan</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>IT'S OK</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Loveland</v>
       </c>
       <c r="G121" t="str">
-        <v>2:19</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Bryson Tiller</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L121" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>earth is turning</v>
+        <v>Fantasy</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G122" t="str">
-        <v>4:49</v>
+        <v>2:21</v>
       </c>
       <c r="H122" t="str">
-        <v>horsegiirL</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L122" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Cool Buzz</v>
+        <v>Already Know</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:32</v>
+        <v>2:37</v>
       </c>
       <c r="H123" t="str">
-        <v>Violet Grohl</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L123" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Better</v>
+        <v>PIECES</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>U</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Baauer</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L124" t="str">
-        <v>Better - Baauer</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ride Lonesome</v>
+        <v>Shimmer</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G125" t="str">
-        <v>4:32</v>
+        <v>2:47</v>
       </c>
       <c r="H125" t="str">
-        <v>Beck</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L125" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Window</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G126" t="str">
-        <v>1:56</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>Billie Eilish</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L126" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Big Mama</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:29</v>
+        <v>3:35</v>
       </c>
       <c r="H127" t="str">
-        <v>Latto</v>
+        <v>Korn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L127" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Born To Die</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Born To Die - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G128" t="str">
-        <v>2:45</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Shaboozey</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L128" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>La Buena</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Florescence</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:08</v>
+        <v>2:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Maisie Peters</v>
+        <v>Carín León</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L129" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Tiny Raisin</v>
+        <v>You Better Know</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Loveland</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G130" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L130" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Fantasy</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:21</v>
+        <v>3:35</v>
       </c>
       <c r="H131" t="str">
-        <v>Demi Lovato</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L131" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Already Know</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>American Stories</v>
       </c>
       <c r="G132" t="str">
-        <v>2:37</v>
+        <v>4:00</v>
       </c>
       <c r="H132" t="str">
-        <v>The Chainsmokers</v>
+        <v>Rostam</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L132" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>PIECES</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:25</v>
+        <v>3:19</v>
       </c>
       <c r="H133" t="str">
-        <v>The Kid LAROI</v>
+        <v>mgk</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L133" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Shimmer</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Toy With Me</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:47</v>
+        <v>2:33</v>
       </c>
       <c r="H134" t="str">
-        <v>Meghan Trainor</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L134" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Window</v>
+        <v>Door</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G135" t="str">
-        <v>3:37</v>
+        <v>3:54</v>
       </c>
       <c r="H135" t="str">
-        <v>Foo Fighters</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L135" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Reward the Scars</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>2:32</v>
       </c>
       <c r="H136" t="str">
-        <v>Korn</v>
+        <v>Ruel</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L136" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Songs About Us</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Songs About Us</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H137" t="str">
-        <v>Jason Aldean</v>
+        <v>MICO</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L137" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>La Buena</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>La Buena - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>Carín León</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L138" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>You Better Know</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:13</v>
+        <v>3:23</v>
       </c>
       <c r="H139" t="str">
-        <v>Ebony Riley</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L139" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Planting Tomatoes</v>
+        <v>car crash</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:35</v>
+        <v>2:40</v>
       </c>
       <c r="H140" t="str">
-        <v>Lucy Dacus</v>
+        <v>jigitz</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L140" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Back of a Truck</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>American Stories</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>4:00</v>
+        <v>3:22</v>
       </c>
       <c r="H141" t="str">
-        <v>Rostam</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L141" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>FIX UR FACE</v>
+        <v>Better Days</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:19</v>
+        <v>3:35</v>
       </c>
       <c r="H142" t="str">
-        <v>mgk</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L142" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>CELEBRATION</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>Location Lost</v>
       </c>
       <c r="G143" t="str">
-        <v>2:33</v>
+        <v>4:32</v>
       </c>
       <c r="H143" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Failure</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L143" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Door</v>
+        <v>Cryogen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G144" t="str">
-        <v>3:54</v>
+        <v>5:01</v>
       </c>
       <c r="H144" t="str">
-        <v>Conan Gray</v>
+        <v>Muse</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L144" t="str">
-        <v>Door - Conan Gray</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Hate Myself</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G145" t="str">
-        <v>2:32</v>
+        <v>1:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Ruel</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L145" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>DREAMBOY</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G146" t="str">
-        <v>3:17</v>
+        <v>3:39</v>
       </c>
       <c r="H146" t="str">
-        <v>MICO</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L146" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>HBO</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:52</v>
+        <v>3:42</v>
       </c>
       <c r="H147" t="str">
-        <v>Daniel Seavey</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L147" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:23</v>
+        <v>3:15</v>
       </c>
       <c r="H148" t="str">
-        <v>The Two Lips</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L148" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>car crash</v>
+        <v>collide</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>car crash - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G149" t="str">
-        <v>2:40</v>
+        <v>3:43</v>
       </c>
       <c r="H149" t="str">
-        <v>jigitz</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L149" t="str">
-        <v>car crash - jigitz</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>All This Disaster</v>
+        <v>freak for you</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>All This Disaster - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:22</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Sarah McLachlan</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L150" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Better Days</v>
+        <v>Anymore</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:35</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L151" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>The Rising Skyline</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Location Lost</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>4:32</v>
+        <v>3:17</v>
       </c>
       <c r="H152" t="str">
-        <v>Failure</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L152" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cryogen</v>
+        <v>oh child</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Wow! Signal</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>5:01</v>
+        <v>2:02</v>
       </c>
       <c r="H153" t="str">
-        <v>Muse</v>
+        <v>kai devega</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L153" t="str">
-        <v>Cryogen - Muse</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:21</v>
+        <v>2:58</v>
       </c>
       <c r="H154" t="str">
-        <v>Nick Cave</v>
+        <v>tbh</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L154" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Dance To This</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>3:39</v>
+        <v>2:54</v>
       </c>
       <c r="H155" t="str">
-        <v>Genesis Owusu</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>HBO</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>HBO - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:42</v>
+        <v>3:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Yung Gravy</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L156" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Need For Speed</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Need For Speed - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G157" t="str">
         <v>3:15</v>
       </c>
       <c r="H157" t="str">
-        <v>Kim Petras</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L157" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>collide</v>
+        <v>Backwards</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H158" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L158" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>freak for you</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>freak for you - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G159" t="str">
-        <v>2:26</v>
+        <v>3:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Haiden Henderson</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L159" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Anymore</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:37</v>
+        <v>3:43</v>
       </c>
       <c r="H160" t="str">
-        <v>Asha Banks</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L160" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Why Am I Here</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:17</v>
+        <v>3:42</v>
       </c>
       <c r="H161" t="str">
-        <v>Presley Regier</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L161" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>oh child</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>oh child - Single</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:02</v>
+        <v>2:59</v>
       </c>
       <c r="H162" t="str">
-        <v>kai devega</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L162" t="str">
-        <v>oh child - kai devega</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Leave Me For Good</v>
+        <v>Tremolo</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G163" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H163" t="str">
-        <v>tbh</v>
+        <v>Metric</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L163" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Dance To This</v>
+        <v>In the Dark</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Ritual</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>3:52</v>
       </c>
       <c r="H164" t="str">
-        <v>Icona Pop</v>
+        <v>Atreyu</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L164" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G165" t="str">
-        <v>3:58</v>
+        <v>4:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Tauren Wells</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L165" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>You Can Have Him</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:09</v>
       </c>
       <c r="H166" t="str">
-        <v>Carly Pearce</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L166" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Backwards</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Backwards - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G167" t="str">
-        <v>3:17</v>
+        <v>4:16</v>
       </c>
       <c r="H167" t="str">
-        <v>Hudson Westbrook</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L167" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Serial Romantic</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>3:27</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L168" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:43</v>
+        <v>3:39</v>
       </c>
       <c r="H169" t="str">
-        <v>Isaiah Falls</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L169" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G170" t="str">
-        <v>3:42</v>
+        <v>2:03</v>
       </c>
       <c r="H170" t="str">
-        <v>PARTYOF2</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L170" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Dance In The USA</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G171" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Show Me the Body</v>
+        <v>Montana 700</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L171" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Tremolo</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Romanticize The Dive</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:43</v>
+        <v>2:31</v>
       </c>
       <c r="H172" t="str">
-        <v>Metric</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L172" t="str">
-        <v>Tremolo - Metric</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>In the Dark</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The End is Not the End</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:52</v>
+        <v>3:28</v>
       </c>
       <c r="H173" t="str">
-        <v>Atreyu</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L173" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>Twice</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G174" t="str">
-        <v>4:36</v>
+        <v>2:32</v>
       </c>
       <c r="H174" t="str">
-        <v>Modest Mouse</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L174" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Saw Your Face</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:09</v>
+        <v>2:36</v>
       </c>
       <c r="H175" t="str">
-        <v>Malcolm Todd</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L175" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Demons In Your Choir</v>
+        <v>hide and seek</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Grateful</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:16</v>
+        <v>2:47</v>
       </c>
       <c r="H176" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L176" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Full Circle</v>
+        <v>Be the One</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:15</v>
+        <v>3:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Leonie Biney</v>
+        <v>Adam Port</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L177" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G178" t="str">
-        <v>3:39</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>Sophia Stel</v>
+        <v>Lane 8</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L178" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>No Invite</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Destined For Greatness</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G179" t="str">
-        <v>2:03</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Luh Tyler</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L179" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>Bando</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Sadetra Son</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G180" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>Montana 700</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L180" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G181" t="str">
         <v>2:31</v>
       </c>
       <c r="H181" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L181" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>Physical</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:28</v>
+        <v>2:40</v>
       </c>
       <c r="H182" t="str">
-        <v>Beach Bunny</v>
+        <v>J. Worra</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L182" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Twice</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:32</v>
+        <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Arrows in Action</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L183" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Asleep Talking</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:36</v>
+        <v>3:37</v>
       </c>
       <c r="H184" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L184" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>hide and seek</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>hide and seek - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Hailey Picardi</v>
+        <v>FEYI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L185" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Be the One</v>
+        <v>Campeones</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Be the One - Single</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:25</v>
+        <v>3:48</v>
       </c>
       <c r="H186" t="str">
-        <v>Adam Port</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L186" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>World Is Mine</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>World Is Mine</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G187" t="str">
-        <v>4:46</v>
+        <v>3:27</v>
       </c>
       <c r="H187" t="str">
-        <v>Lane 8</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L187" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>No Invite</v>
+        <v>tennis practice</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>The Last Balloon</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>2:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Khatumu</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L188" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bando</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>HOPE!!</v>
+        <v>Singing</v>
       </c>
       <c r="G189" t="str">
-        <v>3:17</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L189" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G190" t="str">
-        <v>2:31</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Duke Dumont</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L190" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Physical</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Physical - Single</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G191" t="str">
-        <v>2:40</v>
+        <v>5:54</v>
       </c>
       <c r="H191" t="str">
-        <v>J. Worra</v>
+        <v>Friko</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L191" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>3:19</v>
+        <v>7:05</v>
       </c>
       <c r="H192" t="str">
-        <v>LEGADO 7</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L192" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>AM I OKAY?!</v>
+        <v>Cake</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:37</v>
+        <v>2:36</v>
       </c>
       <c r="H193" t="str">
-        <v>Durand Bernarr</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L193" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Have You Ever</v>
+        <v>from a distance</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Have You Ever - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>FEYI</v>
+        <v>Luz</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L194" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Campeones</v>
+        <v>Second Hand</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Campeones - Single</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:48</v>
+        <v>3:24</v>
       </c>
       <c r="H195" t="str">
-        <v>Cypress Hill</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L195" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G196" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H196" t="str">
-        <v>Mina Tindle</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L196" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>tennis practice</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>exposure therapy - EP</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G197" t="str">
-        <v>2:41</v>
+        <v>2:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Khatumu</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L197" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Moon Not Mine</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Singing</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G198" t="str">
-        <v>3:37</v>
+        <v>3:50</v>
       </c>
       <c r="H198" t="str">
-        <v>Gia Margaret</v>
+        <v>At The Gates</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L198" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>You Say I Love You</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G199" t="str">
-        <v>3:06</v>
+        <v>3:35</v>
       </c>
       <c r="H199" t="str">
-        <v>Quiet Light</v>
+        <v>Sepultura</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L199" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Other Hells</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-29</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Other Hells - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>5:54</v>
+        <v>2:06</v>
       </c>
       <c r="H200" t="str">
-        <v>Friko</v>
+        <v>Ceremony</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
       </c>
       <c r="L200" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>Other Hells - Ceremony</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Hit a Moonshot</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-29</v>
@@ -8013,372 +8013,30 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G201" t="str">
-        <v>7:05</v>
+        <v>4:34</v>
       </c>
       <c r="H201" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
       <c r="L201" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Cake</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Cake - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:36</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Mila Smith</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Cake - Mila Smith</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>from a distance</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>from a distance - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Luz</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
-      </c>
-      <c r="L203" t="str">
-        <v>from a distance - Luz</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Second Hand</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Second Hand - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Anais Cardot</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Second Hand - Anais Cardot</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Mnikeni</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Ku Ngawe</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:08</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Thando Zide</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Mnikeni - Thando Zide</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Lorcan's Song</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:40</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Christian Henson</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>In Dark Distortion</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>The Ghost of a Future Dead</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:50</v>
-      </c>
-      <c r="H207" t="str">
-        <v>At The Gates</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
-      </c>
-      <c r="L207" t="str">
-        <v>In Dark Distortion - At The Gates</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>All Souls Rising</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Sepultura</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
-      </c>
-      <c r="L208" t="str">
-        <v>All Souls Rising - Sepultura</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Other Hells</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Other Hells - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>2:06</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Ceremony</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Other Hells - Ceremony</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Hit a Moonshot</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:34</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
-      </c>
-      <c r="L210" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E201" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>2026-04-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%91%d7%a8-%d7%94%d7%93%d7%a1-%d7%90%d7%9e%d7%90-%d7%9e%d7%9c%d7%9b%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>“אמא מלכה” של רוני בר הדס הוא פופ עכשווי שמצליח להיות גם קליט ושובב  וגם רגשי וכנה מתחת לפני השטח. יש כאן עטיפה מתקתקה, כמעט “מרקידה”, שבתוכה יושב טקסט חשוף על מועקה, בדידות ודימוי עצמי. “יש לי אלף ואחת סיבות</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Keith Urban</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-30</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-30</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Armik</v>
+        <v>Danna</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-30</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Europe</v>
+        <v>Armik</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-30</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v>Europe</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-30</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-30</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Muse</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Muse</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Shaboozey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Scorpions</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Meghan Trainor</v>
+        <v>Scorpions</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Icona Pop</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Jackson</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>The All-American Rejects</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Ringo Starr</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lukas Graham</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Haiden Henderson</v>
+        <v>RUEL</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Foo Fighters</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bublé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Malcolm Todd</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Sam Feldt</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Duran Duran</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danna</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Danna</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Beck</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Digster Pop Music</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Beck</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The All-American Rejects</v>
+        <v>Beck</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madonna</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Freya Ridings</v>
+        <v>Madonna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Celine Dion</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Peter Gabriel</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>ERNEST</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>ERNEST</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dean Lewis</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>Bella White</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Ben Gallaher</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Tyla</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Tyla</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lana Del Rey</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Loreen</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Loreen</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tenille Townes</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic</v>
+        <v>Danna</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Revivalists</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>James Smith</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Holly Humberstone</v>
+        <v>James Smith</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-30</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-30</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-30</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-30</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-30</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Conan Gray</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>TemplesOfficial</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>bleachers</v>
+        <v>Laufey</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>LANY</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>LANY</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-30</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Kygo and carter faith</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>florencemachine</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Scorpions</v>
+        <v>florencemachine</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Mae Muller</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lioness</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Maya Hawke</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Lioness</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kehlani</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G103" t="str">
-        <v>3:06</v>
+        <v>3:32</v>
       </c>
       <c r="H103" t="str">
-        <v>Kehlani</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L103" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Después de ti</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Después de ti - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G104" t="str">
-        <v>4:35</v>
+        <v>3:06</v>
       </c>
       <c r="H104" t="str">
-        <v>KAROL G</v>
+        <v>Kehlani</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L104" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dando Vueltas</v>
+        <v>Después de ti</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:12</v>
+        <v>4:35</v>
       </c>
       <c r="H105" t="str">
-        <v>Rauw Alejandro</v>
+        <v>KAROL G</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L105" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Doors</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:51</v>
+        <v>3:12</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L106" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Doors</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G107" t="str">
-        <v>3:48</v>
+        <v>3:51</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Langley</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L107" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Todos nos Shipean</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H108" t="str">
-        <v>Fuerza Regida</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L108" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Ojitos Bellos</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:59</v>
+        <v>2:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Grupo Frontera</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L109" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>REDRED</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>2:59</v>
       </c>
       <c r="H110" t="str">
-        <v>CORTIS</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L110" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Little More Time</v>
+        <v>REDRED</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dinner Party</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G111" t="str">
-        <v>3:38</v>
+        <v>2:43</v>
       </c>
       <c r="H111" t="str">
-        <v>Niall Horan</v>
+        <v>CORTIS</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L111" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>IT'S OK</v>
+        <v>Little More Time</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G112" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>Bryson Tiller</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L112" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>earth is turning</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>2:19</v>
       </c>
       <c r="H113" t="str">
-        <v>horsegiirL</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L113" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cool Buzz</v>
+        <v>earth is turning</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Be Sweet To Me</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G114" t="str">
-        <v>2:32</v>
+        <v>4:49</v>
       </c>
       <c r="H114" t="str">
-        <v>Violet Grohl</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L114" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Better</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>U</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G115" t="str">
-        <v>3:50</v>
+        <v>2:32</v>
       </c>
       <c r="H115" t="str">
-        <v>Baauer</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L115" t="str">
-        <v>Better - Baauer</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G116" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H116" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L116" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H117" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L118" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G119" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H119" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L119" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L120" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L121" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G122" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H122" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L122" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H123" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L123" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H124" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L124" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G125" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L125" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L126" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G127" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H127" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L127" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H128" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L128" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G129" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H129" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L129" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L130" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G131" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L131" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L132" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G133" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H133" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L133" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H134" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L134" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H135" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L135" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G136" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L136" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H137" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L137" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L138" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H139" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H140" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L140" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H141" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L141" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H142" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L142" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G143" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L143" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G144" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H144" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L144" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G145" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H145" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L145" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H146" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L146" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G147" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L147" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L148" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L149" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H150" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L150" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H151" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L151" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L152" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H153" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L153" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Leave Me For Good</v>
+        <v>oh child</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:58</v>
+        <v>2:02</v>
       </c>
       <c r="H154" t="str">
-        <v>tbh</v>
+        <v>kai devega</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L154" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Dance To This</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>tbh</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L155" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G156" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H156" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L156" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H157" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L157" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L158" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H159" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L159" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G160" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L160" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H161" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L161" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H162" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L162" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H163" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L163" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G164" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H164" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L164" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G165" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L165" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G166" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H166" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L166" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H167" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L167" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L168" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L169" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H170" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L170" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H171" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L171" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G172" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L172" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H174" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L174" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G175" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H175" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L175" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H176" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L176" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H177" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L177" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L178" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Invite</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>The Last Balloon</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G179" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Lane 8</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L179" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bando</v>
+        <v>No Invite</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HOPE!!</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L180" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Bando</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G181" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>Duke Dumont</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Physical</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Physical - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H182" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L182" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H183" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H184" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L184" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H185" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L185" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H186" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L186" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L187" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G188" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H188" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L188" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L189" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H190" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L190" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G191" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H191" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L191" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G192" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H192" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L192" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H193" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L193" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H194" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L194" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L195" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H196" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L196" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G197" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H197" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L197" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G198" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H198" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L198" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G199" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H199" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L199" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-30</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G200" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H200" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L200" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-30</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>4:34</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רוני בר הדס – אמא מלכה</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-30</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%91%d7%a8-%d7%94%d7%93%d7%a1-%d7%90%d7%9e%d7%90-%d7%9e%d7%9c%d7%9b%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“אמא מלכה” של רוני בר הדס הוא פופ עכשווי שמצליח להיות גם קליט ושובב  וגם רגשי וכנה מתחת לפני השטח. יש כאן עטיפה מתקתקה, כמעט “מרקידה”, שבתוכה יושב טקסט חשוף על מועקה, בדידות ודימוי עצמי. “יש לי אלף ואחת סיבות</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רוני בר הדס – אמא מלכה</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>19h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-30</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Keith Urban</v>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-30</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Danna</v>
+        <v>Armik</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-30</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Armik</v>
+        <v>Europe</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-30</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Europe</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-30</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Foo Fighters</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-30</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Muse</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Muse</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Shaboozey</v>
+        <v>Scorpions</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Scorpions</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Icona Pop</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Michael Jackson</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The All-American Rejects</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Ringo Starr</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Demi Lovato</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dean Lewis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Ella Langley</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Lukas Graham</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Foo Fighters</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>RUEL</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Haiden Henderson</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Conan Gray</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Foo Fighters</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ringo Starr</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Michael Bublé</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Malcolm Todd</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Sam Feldt</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Niall Horan</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Duran Duran</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Freya Skye</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Danna</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Danna</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Cannons</v>
+        <v>Beck</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Beck</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Digster Pop Music</v>
+        <v>Beck</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Beck</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The All-American Rejects</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Demi Lovato</v>
+        <v>Madonna</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madonna</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Freya Ridings</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Celine Dion</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Peter Gabriel</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Jessie Ware</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>The Kid LAROI.</v>
+        <v>ERNEST</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>ERNEST</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Bella White</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Kip Moore</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Ben Gallaher</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Johnny Orlando</v>
+        <v>Tyla</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Tyla</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Lana Del Rey</v>
+        <v>Loreen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Loreen</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Tenille Townes</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Danna</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>OneRepublic</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>The Revivalists</v>
+        <v>James Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>James Smith</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-30</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ava Max</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-30</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-30</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-30</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Ava Max</v>
+        <v>Danna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-30</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Conan Gray</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>TemplesOfficial</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Laufey</v>
+        <v>bleachers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>bleachers</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Nothing But Thieves</v>
+        <v>LANY</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>LANY</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-30</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kygo and carter faith</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>florencemachine</v>
+        <v>Scorpions</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Holly Humberstone</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Lioness</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H102" t="str">
-        <v>Mae Muller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L102" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Lioness</v>
+        <v>Shoulda Never (feat. Usher)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Kehlani</v>
       </c>
       <c r="G103" t="str">
-        <v>3:32</v>
+        <v>3:06</v>
       </c>
       <c r="H103" t="str">
-        <v>Maya Hawke</v>
+        <v>Kehlani</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
       </c>
       <c r="L103" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Shoulda Never (feat. Usher) - Kehlani</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Shoulda Never (feat. Usher)</v>
+        <v>Después de ti</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/shoulda-never-feat-usher/1885055419</v>
+        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Kehlani</v>
+        <v>Después de ti - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:06</v>
+        <v>4:35</v>
       </c>
       <c r="H104" t="str">
-        <v>Kehlani</v>
+        <v>KAROL G</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/shoulda-never-feat-usher/1885055310</v>
+        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
       </c>
       <c r="L104" t="str">
-        <v>Shoulda Never (feat. Usher) - Kehlani</v>
+        <v>Después de ti - KAROL G</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Después de ti</v>
+        <v>Dando Vueltas</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/despu%C3%A9s-de-ti/6763361584</v>
+        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Después de ti - Single</v>
+        <v>Dando Vueltas - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:35</v>
+        <v>3:12</v>
       </c>
       <c r="H105" t="str">
-        <v>KAROL G</v>
+        <v>Rauw Alejandro</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/karol-g/290814601</v>
+        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/despu%C3%A9s-de-ti/1895280426</v>
+        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
       </c>
       <c r="L105" t="str">
-        <v>Después de ti - KAROL G</v>
+        <v>Dando Vueltas - Rauw Alejandro</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Dando Vueltas</v>
+        <v>Doors</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/dando-vueltas/1893775786</v>
+        <v>https://music.apple.com/us/song/doors/1872239879</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dando Vueltas - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v>3:12</v>
+        <v>3:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Rauw Alejandro</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/rauw-alejandro/1107186883</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/dando-vueltas/1893775784</v>
+        <v>https://music.apple.com/us/album/doors/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>Dando Vueltas - Rauw Alejandro</v>
+        <v>Doors - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Doors</v>
+        <v>I Can't Love You Anymore</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/doors/1872239879</v>
+        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Great Divide</v>
+        <v>I Can't Love You Anymore - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:51</v>
+        <v>3:48</v>
       </c>
       <c r="H107" t="str">
-        <v>Noah Kahan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/doors/1872239868</v>
+        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
       </c>
       <c r="L107" t="str">
-        <v>Doors - Noah Kahan</v>
+        <v>I Can't Love You Anymore - Ella Langley</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Can't Love You Anymore</v>
+        <v>Todos nos Shipean</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-cant-love-you-anymore/6763091996</v>
+        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>I Can't Love You Anymore - Single</v>
+        <v>Todos nos Shipean - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:48</v>
+        <v>2:16</v>
       </c>
       <c r="H108" t="str">
-        <v>Ella Langley</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-cant-love-you-anymore/1895158676</v>
+        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
       </c>
       <c r="L108" t="str">
-        <v>I Can't Love You Anymore - Ella Langley</v>
+        <v>Todos nos Shipean - Fuerza Regida</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Todos nos Shipean</v>
+        <v>Ojitos Bellos</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/todos-nos-shipean/6762561698</v>
+        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Todos nos Shipean - Single</v>
+        <v>Ojitos Bellos - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:16</v>
+        <v>2:59</v>
       </c>
       <c r="H109" t="str">
-        <v>Fuerza Regida</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/todos-nos-shipean/1894682278</v>
+        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
       </c>
       <c r="L109" t="str">
-        <v>Todos nos Shipean - Fuerza Regida</v>
+        <v>Ojitos Bellos - Grupo Frontera</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ojitos Bellos</v>
+        <v>REDRED</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ojitos-bellos/1894300931</v>
+        <v>https://music.apple.com/us/song/redred/1887671067</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ojitos Bellos - Single</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G110" t="str">
-        <v>2:59</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Grupo Frontera</v>
+        <v>CORTIS</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ojitos-bellos/1894300930</v>
+        <v>https://music.apple.com/us/album/redred/1887671065</v>
       </c>
       <c r="L110" t="str">
-        <v>Ojitos Bellos - Grupo Frontera</v>
+        <v>REDRED - CORTIS</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>REDRED</v>
+        <v>Little More Time</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/redred/1887671067</v>
+        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G111" t="str">
-        <v>2:43</v>
+        <v>3:38</v>
       </c>
       <c r="H111" t="str">
-        <v>CORTIS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/redred/1887671065</v>
+        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
       </c>
       <c r="L111" t="str">
-        <v>REDRED - CORTIS</v>
+        <v>Little More Time - Niall Horan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Little More Time</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/little-more-time/1884418592</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Dinner Party</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H112" t="str">
-        <v>Niall Horan</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/little-more-time/1884418567</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L112" t="str">
-        <v>Little More Time - Niall Horan</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>IT'S OK</v>
+        <v>earth is turning</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>IT'S OK - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G113" t="str">
-        <v>2:19</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Bryson Tiller</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
       </c>
       <c r="L113" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>earth is turning - horsegiirL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>earth is turning</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/earth-is-turning/1893373640</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G114" t="str">
-        <v>4:49</v>
+        <v>2:32</v>
       </c>
       <c r="H114" t="str">
-        <v>horsegiirL</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/earth-is-turning/1893373426</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L114" t="str">
-        <v>earth is turning - horsegiirL</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Cool Buzz</v>
+        <v>Better</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Be Sweet To Me</v>
+        <v>U</v>
       </c>
       <c r="G115" t="str">
-        <v>2:32</v>
+        <v>3:50</v>
       </c>
       <c r="H115" t="str">
-        <v>Violet Grohl</v>
+        <v>Baauer</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L115" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Better</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/better/1885858065</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>U</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:50</v>
+        <v>4:32</v>
       </c>
       <c r="H116" t="str">
-        <v>Baauer</v>
+        <v>Beck</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/baauer/526199085</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/better/1885857722</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L116" t="str">
-        <v>Better - Baauer</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ride Lonesome</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:32</v>
+        <v>1:56</v>
       </c>
       <c r="H117" t="str">
-        <v>Beck</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L117" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G118" t="str">
-        <v>1:56</v>
+        <v>2:29</v>
       </c>
       <c r="H118" t="str">
-        <v>Billie Eilish</v>
+        <v>Latto</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L118" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Big Mama</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:29</v>
+        <v>2:45</v>
       </c>
       <c r="H119" t="str">
-        <v>Latto</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L119" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Born To Die</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Born To Die - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>2:45</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>Shaboozey</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Florescence</v>
+        <v>Loveland</v>
       </c>
       <c r="G121" t="str">
-        <v>3:08</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Maisie Peters</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L121" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tiny Raisin</v>
+        <v>Fantasy</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Loveland</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:58</v>
+        <v>2:21</v>
       </c>
       <c r="H122" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L122" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Fantasy</v>
+        <v>Already Know</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:21</v>
+        <v>2:37</v>
       </c>
       <c r="H123" t="str">
-        <v>Demi Lovato</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L123" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Already Know</v>
+        <v>PIECES</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:37</v>
+        <v>3:25</v>
       </c>
       <c r="H124" t="str">
-        <v>The Chainsmokers</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L124" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PIECES</v>
+        <v>Shimmer</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G125" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H125" t="str">
-        <v>The Kid LAROI</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L125" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Shimmer</v>
+        <v>Window</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Toy With Me</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>Meghan Trainor</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L126" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Window</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H127" t="str">
-        <v>Foo Fighters</v>
+        <v>Korn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L127" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Reward the Scars</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G128" t="str">
-        <v>3:35</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Korn</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L128" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Songs About Us</v>
+        <v>La Buena</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Songs About Us</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Jason Aldean</v>
+        <v>Carín León</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L129" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>La Buena</v>
+        <v>You Better Know</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>La Buena - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G130" t="str">
-        <v>2:16</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Carín León</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L130" t="str">
-        <v>La Buena - Carín León</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>You Better Know</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:13</v>
+        <v>3:35</v>
       </c>
       <c r="H131" t="str">
-        <v>Ebony Riley</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L131" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Planting Tomatoes</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G132" t="str">
-        <v>3:35</v>
+        <v>4:00</v>
       </c>
       <c r="H132" t="str">
-        <v>Lucy Dacus</v>
+        <v>Rostam</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L132" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Back of a Truck</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>American Stories</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:00</v>
+        <v>3:19</v>
       </c>
       <c r="H133" t="str">
-        <v>Rostam</v>
+        <v>mgk</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L133" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FIX UR FACE</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:19</v>
+        <v>2:33</v>
       </c>
       <c r="H134" t="str">
-        <v>mgk</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L134" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CELEBRATION</v>
+        <v>Door</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G135" t="str">
-        <v>2:33</v>
+        <v>3:54</v>
       </c>
       <c r="H135" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L135" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Door</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:54</v>
+        <v>2:32</v>
       </c>
       <c r="H136" t="str">
-        <v>Conan Gray</v>
+        <v>Ruel</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L136" t="str">
-        <v>Door - Conan Gray</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Hate Myself</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Hate Myself - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:32</v>
+        <v>3:17</v>
       </c>
       <c r="H137" t="str">
-        <v>Ruel</v>
+        <v>MICO</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L137" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>DREAMBOY</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:17</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>MICO</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L138" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:52</v>
+        <v>3:23</v>
       </c>
       <c r="H139" t="str">
-        <v>Daniel Seavey</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L139" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>car crash</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:23</v>
+        <v>2:40</v>
       </c>
       <c r="H140" t="str">
-        <v>The Two Lips</v>
+        <v>jigitz</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L140" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>car crash</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>car crash - Single</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:40</v>
+        <v>3:22</v>
       </c>
       <c r="H141" t="str">
-        <v>jigitz</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L141" t="str">
-        <v>car crash - jigitz</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>All This Disaster</v>
+        <v>Better Days</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>All This Disaster - Single</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:22</v>
+        <v>3:35</v>
       </c>
       <c r="H142" t="str">
-        <v>Sarah McLachlan</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L142" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Better Days</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>Location Lost</v>
       </c>
       <c r="G143" t="str">
-        <v>3:35</v>
+        <v>4:32</v>
       </c>
       <c r="H143" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Failure</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L143" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Rising Skyline</v>
+        <v>Cryogen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Location Lost</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G144" t="str">
-        <v>4:32</v>
+        <v>5:01</v>
       </c>
       <c r="H144" t="str">
-        <v>Failure</v>
+        <v>Muse</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L144" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Cryogen</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Wow! Signal</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G145" t="str">
-        <v>5:01</v>
+        <v>1:21</v>
       </c>
       <c r="H145" t="str">
-        <v>Muse</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L145" t="str">
-        <v>Cryogen - Muse</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Harry Hole Theme</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G146" t="str">
-        <v>1:21</v>
+        <v>3:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Nick Cave</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L146" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>HBO</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>3:42</v>
       </c>
       <c r="H147" t="str">
-        <v>Genesis Owusu</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L147" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>HBO</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HBO - Single</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>3:15</v>
       </c>
       <c r="H148" t="str">
-        <v>Yung Gravy</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L148" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Need For Speed</v>
+        <v>collide</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Need For Speed - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G149" t="str">
-        <v>3:15</v>
+        <v>3:43</v>
       </c>
       <c r="H149" t="str">
-        <v>Kim Petras</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L149" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>collide</v>
+        <v>freak for you</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>girls like girls (the album)</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:43</v>
+        <v>2:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L150" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>freak for you</v>
+        <v>Anymore</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>freak for you - Single</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:26</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Haiden Henderson</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L151" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Anymore</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:37</v>
+        <v>3:17</v>
       </c>
       <c r="H152" t="str">
-        <v>Asha Banks</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L152" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Why Am I Here</v>
+        <v>oh child</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:17</v>
+        <v>2:02</v>
       </c>
       <c r="H153" t="str">
-        <v>Presley Regier</v>
+        <v>kai devega</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L153" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>oh child</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>oh child - Single</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:02</v>
+        <v>2:58</v>
       </c>
       <c r="H154" t="str">
-        <v>kai devega</v>
+        <v>tbh</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L154" t="str">
-        <v>oh child - kai devega</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Leave Me For Good</v>
+        <v>Dance To This</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>2:58</v>
+        <v>2:54</v>
       </c>
       <c r="H155" t="str">
-        <v>tbh</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Dance To This</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ritual</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:54</v>
+        <v>3:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Icona Pop</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L156" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:58</v>
+        <v>3:15</v>
       </c>
       <c r="H157" t="str">
-        <v>Tauren Wells</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L157" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>You Can Have Him</v>
+        <v>Backwards</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:15</v>
+        <v>3:17</v>
       </c>
       <c r="H158" t="str">
-        <v>Carly Pearce</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L158" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Backwards</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Backwards - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G159" t="str">
-        <v>3:17</v>
+        <v>3:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L159" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Love Ain't Shit</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Serial Romantic</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:27</v>
+        <v>3:43</v>
       </c>
       <c r="H160" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L160" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:43</v>
+        <v>3:42</v>
       </c>
       <c r="H161" t="str">
-        <v>Isaiah Falls</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L161" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H162" t="str">
-        <v>PARTYOF2</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L162" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Dance In The USA</v>
+        <v>Tremolo</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G163" t="str">
-        <v>2:59</v>
+        <v>3:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Show Me the Body</v>
+        <v>Metric</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L163" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Tremolo</v>
+        <v>In the Dark</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Romanticize The Dive</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G164" t="str">
-        <v>3:43</v>
+        <v>3:52</v>
       </c>
       <c r="H164" t="str">
-        <v>Metric</v>
+        <v>Atreyu</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L164" t="str">
-        <v>Tremolo - Metric</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>In the Dark</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>The End is Not the End</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G165" t="str">
-        <v>3:52</v>
+        <v>4:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Atreyu</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L165" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:36</v>
+        <v>3:09</v>
       </c>
       <c r="H166" t="str">
-        <v>Modest Mouse</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L166" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>I Saw Your Face</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G167" t="str">
-        <v>3:09</v>
+        <v>4:16</v>
       </c>
       <c r="H167" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L167" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Demons In Your Choir</v>
+        <v>Full Circle</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Grateful</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>4:16</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L168" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Full Circle</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:15</v>
+        <v>3:39</v>
       </c>
       <c r="H169" t="str">
-        <v>Leonie Biney</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L169" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G170" t="str">
-        <v>3:39</v>
+        <v>2:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Sophia Stel</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L170" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Destined For Greatness</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G171" t="str">
-        <v>2:03</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>Luh Tyler</v>
+        <v>Montana 700</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L171" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Sadetra Son</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>2:31</v>
       </c>
       <c r="H172" t="str">
-        <v>Montana 700</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L172" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:31</v>
+        <v>3:28</v>
       </c>
       <c r="H173" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L173" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>Twice</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G174" t="str">
-        <v>3:28</v>
+        <v>2:32</v>
       </c>
       <c r="H174" t="str">
-        <v>Beach Bunny</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L174" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Twice</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:32</v>
+        <v>2:36</v>
       </c>
       <c r="H175" t="str">
-        <v>Arrows in Action</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L175" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Asleep Talking</v>
+        <v>hide and seek</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:36</v>
+        <v>2:47</v>
       </c>
       <c r="H176" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L176" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>hide and seek</v>
+        <v>Be the One</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>hide and seek - Single</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Hailey Picardi</v>
+        <v>Adam Port</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L177" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Be the One</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Be the One - Single</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G178" t="str">
-        <v>3:25</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>Adam Port</v>
+        <v>Lane 8</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L178" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>World Is Mine</v>
+        <v>No Invite</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>World Is Mine</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G179" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Lane 8</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L179" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>No Invite</v>
+        <v>Bando</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>The Last Balloon</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G180" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L180" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Bando</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>HOPE!!</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>2:31</v>
       </c>
       <c r="H181" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L181" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Physical</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:31</v>
+        <v>2:40</v>
       </c>
       <c r="H182" t="str">
-        <v>Duke Dumont</v>
+        <v>J. Worra</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L182" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Physical</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Physical - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:40</v>
+        <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>J. Worra</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L183" t="str">
-        <v>Physical - J. Worra</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:19</v>
+        <v>3:37</v>
       </c>
       <c r="H184" t="str">
-        <v>LEGADO 7</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L184" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>AM I OKAY?!</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Durand Bernarr</v>
+        <v>FEYI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L185" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Have You Ever</v>
+        <v>Campeones</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Have You Ever - Single</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H186" t="str">
-        <v>FEYI</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L186" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Campeones</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Campeones - Single</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G187" t="str">
-        <v>3:48</v>
+        <v>3:27</v>
       </c>
       <c r="H187" t="str">
-        <v>Cypress Hill</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L187" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>tennis practice</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Mina Tindle</v>
+        <v>Khatumu</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L188" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>tennis practice</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Singing</v>
       </c>
       <c r="G189" t="str">
-        <v>2:41</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Khatumu</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L189" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Moon Not Mine</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Singing</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G190" t="str">
-        <v>3:37</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Gia Margaret</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L190" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>You Say I Love You</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G191" t="str">
-        <v>3:06</v>
+        <v>5:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Quiet Light</v>
+        <v>Friko</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L191" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>5:54</v>
+        <v>7:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Friko</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L192" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Cake</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>7:05</v>
+        <v>2:36</v>
       </c>
       <c r="H193" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L193" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Cake</v>
+        <v>from a distance</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Cake - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:36</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Mila Smith</v>
+        <v>Luz</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L194" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>from a distance</v>
+        <v>Second Hand</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>from a distance - Single</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H195" t="str">
-        <v>Luz</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L195" t="str">
-        <v>from a distance - Luz</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Second Hand</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Second Hand - Single</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G196" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H196" t="str">
-        <v>Anais Cardot</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L196" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Mnikeni</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Ku Ngawe</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G197" t="str">
-        <v>3:08</v>
+        <v>2:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Thando Zide</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L197" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Lorcan's Song</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G198" t="str">
-        <v>2:40</v>
+        <v>3:50</v>
       </c>
       <c r="H198" t="str">
-        <v>Christian Henson</v>
+        <v>At The Gates</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L198" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>In Dark Distortion</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G199" t="str">
-        <v>3:50</v>
+        <v>3:35</v>
       </c>
       <c r="H199" t="str">
-        <v>At The Gates</v>
+        <v>Sepultura</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L199" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>All Souls Rising</v>
+        <v>Other Hells</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-30</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>Other Hells - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:35</v>
+        <v>2:06</v>
       </c>
       <c r="H200" t="str">
-        <v>Sepultura</v>
+        <v>Ceremony</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
       </c>
       <c r="L200" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>Other Hells - Ceremony</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Other Hells</v>
+        <v>Hit a Moonshot</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-30</v>
@@ -8013,68 +8013,30 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Other Hells - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G201" t="str">
-        <v>2:06</v>
+        <v>4:34</v>
       </c>
       <c r="H201" t="str">
-        <v>Ceremony</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
       <c r="L201" t="str">
-        <v>Other Hells - Ceremony</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Hit a Moonshot</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-04-30</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G202" t="str">
-        <v>4:34</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
-      </c>
-      <c r="L202" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>

--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -781,7 +781,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lioness</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-30</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Victory</v>
       </c>
       <c r="G102" t="str">
-        <v>3:32</v>
+        <v>3:27</v>
       </c>
       <c r="H102" t="str">
-        <v>Maya Hawke</v>
+        <v>Madeon</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L102" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="103">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-30</v>
@@ -4631,25 +4631,25 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G112" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H112" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L112" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="113">
@@ -4692,13 +4692,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cool Buzz</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-30</v>
@@ -4707,25 +4707,25 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Be Sweet To Me</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:32</v>
+        <v>2:19</v>
       </c>
       <c r="H114" t="str">
-        <v>Violet Grohl</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L114" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="115">
@@ -4768,13 +4768,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ride Lonesome</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G116" t="str">
-        <v>4:32</v>
+        <v>2:32</v>
       </c>
       <c r="H116" t="str">
-        <v>Beck</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L116" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>1:56</v>
+        <v>4:32</v>
       </c>
       <c r="H117" t="str">
-        <v>Billie Eilish</v>
+        <v>Beck</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L117" t="str">
-        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>GOMF (feat. GloRilla)</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
+        <v>https://music.apple.com/us/song/intro-hit-me-hard-and-soft-tour/6762943480</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Big Mama</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:29</v>
+        <v>1:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Latto</v>
+        <v>Billie Eilish</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/billie-eilish/1065981054</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
+        <v>https://music.apple.com/us/album/intro-hit-me-hard-and-soft-tour/1895089347</v>
       </c>
       <c r="L118" t="str">
-        <v>GOMF (feat. GloRilla) - Latto</v>
+        <v>INTRO (HIT ME HARD AND SOFT TOUR) - Billie Eilish</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Born To Die</v>
+        <v>GOMF (feat. GloRilla)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
+        <v>https://music.apple.com/us/song/gomf-feat-glorilla/1886539101</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Born To Die - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G119" t="str">
-        <v>2:45</v>
+        <v>2:29</v>
       </c>
       <c r="H119" t="str">
-        <v>Shaboozey</v>
+        <v>Latto</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
+        <v>https://music.apple.com/us/album/gomf-feat-glorilla/1886538932</v>
       </c>
       <c r="L119" t="str">
-        <v>Born To Die - Shaboozey</v>
+        <v>GOMF (feat. GloRilla) - Latto</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Kingmaker (with Julia Michaels)</v>
+        <v>Born To Die</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
+        <v>https://music.apple.com/us/song/born-to-die/1893751670</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Born To Die - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
+        <v>https://music.apple.com/us/album/born-to-die/1893751669</v>
       </c>
       <c r="L120" t="str">
-        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
+        <v>Born To Die - Shaboozey</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Tiny Raisin</v>
+        <v>Kingmaker (with Julia Michaels)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
+        <v>https://music.apple.com/us/song/kingmaker-with-julia-michaels/1871502692</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Loveland</v>
+        <v>Florescence</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
+        <v>https://music.apple.com/us/album/kingmaker-with-julia-michaels/1871502372</v>
       </c>
       <c r="L121" t="str">
-        <v>Tiny Raisin - Suki Waterhouse</v>
+        <v>Kingmaker (with Julia Michaels) - Maisie Peters</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Fantasy</v>
+        <v>Tiny Raisin</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
+        <v>https://music.apple.com/us/song/tiny-raisin/1894103383</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>It's Not That Deep (Unless You Want It To Be)</v>
+        <v>Loveland</v>
       </c>
       <c r="G122" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H122" t="str">
-        <v>Demi Lovato</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
+        <v>https://music.apple.com/us/album/tiny-raisin/1894103117</v>
       </c>
       <c r="L122" t="str">
-        <v>Fantasy - Demi Lovato</v>
+        <v>Tiny Raisin - Suki Waterhouse</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Already Know</v>
+        <v>Fantasy</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/already-know/1894074884</v>
+        <v>https://music.apple.com/us/song/fantasy/1894043521</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>It's Not That Deep (Unless You Want It To Be)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:37</v>
+        <v>2:21</v>
       </c>
       <c r="H123" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/already-know/1894074877</v>
+        <v>https://music.apple.com/us/album/fantasy/1894043516</v>
       </c>
       <c r="L123" t="str">
-        <v>Already Know - The Chainsmokers</v>
+        <v>Fantasy - Demi Lovato</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PIECES</v>
+        <v>Already Know</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pieces/6762908054</v>
+        <v>https://music.apple.com/us/song/already-know/1894074884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>BEFORE I FORGET (DELUXE)</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>3:25</v>
+        <v>2:37</v>
       </c>
       <c r="H124" t="str">
-        <v>The Kid LAROI</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pieces/1895071326</v>
+        <v>https://music.apple.com/us/album/already-know/1894074877</v>
       </c>
       <c r="L124" t="str">
-        <v>PIECES - The Kid LAROI</v>
+        <v>Already Know - The Chainsmokers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shimmer</v>
+        <v>PIECES</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
+        <v>https://music.apple.com/us/song/pieces/6762908054</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Toy With Me</v>
+        <v>BEFORE I FORGET (DELUXE)</v>
       </c>
       <c r="G125" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
+        <v>https://music.apple.com/us/album/pieces/1895071326</v>
       </c>
       <c r="L125" t="str">
-        <v>Shimmer - Meghan Trainor</v>
+        <v>PIECES - The Kid LAROI</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Window</v>
+        <v>Shimmer</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/window/1877913733</v>
+        <v>https://music.apple.com/us/song/shimmer/1852006243</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/window/1877913489</v>
+        <v>https://music.apple.com/us/album/shimmer/1852006222</v>
       </c>
       <c r="L126" t="str">
-        <v>Window - Foo Fighters</v>
+        <v>Shimmer - Meghan Trainor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Reward the Scars</v>
+        <v>Window</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
+        <v>https://music.apple.com/us/song/window/1877913733</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Reward the Scars - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G127" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H127" t="str">
-        <v>Korn</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/korn/466532</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
+        <v>https://music.apple.com/us/album/window/1877913489</v>
       </c>
       <c r="L127" t="str">
-        <v>Reward the Scars - Korn</v>
+        <v>Window - Foo Fighters</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
+        <v>https://music.apple.com/us/song/reward-the-scars/1893159528</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Songs About Us</v>
+        <v>Reward the Scars - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H128" t="str">
-        <v>Jason Aldean</v>
+        <v>Korn</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
+        <v>https://music.apple.com/us/artist/korn/466532</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
+        <v>https://music.apple.com/us/album/reward-the-scars/1893159527</v>
       </c>
       <c r="L128" t="str">
-        <v>Songs About Us - Jason Aldean</v>
+        <v>Reward the Scars - Korn</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>La Buena</v>
+        <v>Songs About Us</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
+        <v>https://music.apple.com/us/song/songs-about-us/1847440971</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>La Buena - Single</v>
+        <v>Songs About Us</v>
       </c>
       <c r="G129" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H129" t="str">
-        <v>Carín León</v>
+        <v>Jason Aldean</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/jason-aldean/63684710</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
+        <v>https://music.apple.com/us/album/songs-about-us/1847440777</v>
       </c>
       <c r="L129" t="str">
-        <v>La Buena - Carín León</v>
+        <v>Songs About Us - Jason Aldean</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>You Better Know</v>
+        <v>La Buena</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
+        <v>https://music.apple.com/us/song/la-buena/1891737908</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Beautiful Tragedy</v>
+        <v>La Buena - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Ebony Riley</v>
+        <v>Carín León</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
+        <v>https://music.apple.com/us/album/la-buena/1891737906</v>
       </c>
       <c r="L130" t="str">
-        <v>You Better Know - Ebony Riley</v>
+        <v>La Buena - Carín León</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Planting Tomatoes</v>
+        <v>You Better Know</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
+        <v>https://music.apple.com/us/song/you-better-know/1891409411</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Planting Tomatoes - Single</v>
+        <v>Beautiful Tragedy</v>
       </c>
       <c r="G131" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Lucy Dacus</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
+        <v>https://music.apple.com/us/album/you-better-know/1891409072</v>
       </c>
       <c r="L131" t="str">
-        <v>Planting Tomatoes - Lucy Dacus</v>
+        <v>You Better Know - Ebony Riley</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Back of a Truck</v>
+        <v>Planting Tomatoes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
+        <v>https://music.apple.com/us/song/planting-tomatoes/1891521785</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>American Stories</v>
+        <v>Planting Tomatoes - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:00</v>
+        <v>3:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Rostam</v>
+        <v>Lucy Dacus</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/lucy-dacus/1060812309</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
+        <v>https://music.apple.com/us/album/planting-tomatoes/1891521559</v>
       </c>
       <c r="L132" t="str">
-        <v>Back of a Truck - Rostam</v>
+        <v>Planting Tomatoes - Lucy Dacus</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FIX UR FACE</v>
+        <v>Back of a Truck</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
+        <v>https://music.apple.com/us/song/back-of-a-truck/1876952753</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FIX UR FACE - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G133" t="str">
-        <v>3:19</v>
+        <v>4:00</v>
       </c>
       <c r="H133" t="str">
-        <v>mgk</v>
+        <v>Rostam</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
+        <v>https://music.apple.com/us/album/back-of-a-truck/1876952750</v>
       </c>
       <c r="L133" t="str">
-        <v>FIX UR FACE - mgk</v>
+        <v>Back of a Truck - Rostam</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>CELEBRATION</v>
+        <v>FIX UR FACE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/celebration/1894107708</v>
+        <v>https://music.apple.com/us/song/fix-ur-face/1893808779</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>CELEBRATION - Single</v>
+        <v>FIX UR FACE - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:33</v>
+        <v>3:19</v>
       </c>
       <c r="H134" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/celebration/1894107702</v>
+        <v>https://music.apple.com/us/album/fix-ur-face/1893808777</v>
       </c>
       <c r="L134" t="str">
-        <v>CELEBRATION - LE SSERAFIM</v>
+        <v>FIX UR FACE - mgk</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Door</v>
+        <v>CELEBRATION</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/door/1886835081</v>
+        <v>https://music.apple.com/us/song/celebration/1894107708</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Wishbone Deluxe</v>
+        <v>CELEBRATION - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H135" t="str">
-        <v>Conan Gray</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/door/1886835064</v>
+        <v>https://music.apple.com/us/album/celebration/1894107702</v>
       </c>
       <c r="L135" t="str">
-        <v>Door - Conan Gray</v>
+        <v>CELEBRATION - LE SSERAFIM</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hate Myself</v>
+        <v>Door</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
+        <v>https://music.apple.com/us/song/door/1886835081</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Hate Myself - Single</v>
+        <v>Wishbone Deluxe</v>
       </c>
       <c r="G136" t="str">
-        <v>2:32</v>
+        <v>3:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Ruel</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
+        <v>https://music.apple.com/us/album/door/1886835064</v>
       </c>
       <c r="L136" t="str">
-        <v>Hate Myself - Ruel</v>
+        <v>Door - Conan Gray</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>DREAMBOY</v>
+        <v>Hate Myself</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
+        <v>https://music.apple.com/us/song/hate-myself/1891348564</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>DREAMBOY - Single</v>
+        <v>Hate Myself - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H137" t="str">
-        <v>MICO</v>
+        <v>Ruel</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
+        <v>https://music.apple.com/us/album/hate-myself/1891348562</v>
       </c>
       <c r="L137" t="str">
-        <v>DREAMBOY - MICO</v>
+        <v>Hate Myself - Ruel</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Time to Time (Annie)</v>
+        <v>DREAMBOY</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
+        <v>https://music.apple.com/us/song/dreamboy/1892181648</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Time to Time (Annie) - Single</v>
+        <v>DREAMBOY - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Daniel Seavey</v>
+        <v>MICO</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
+        <v>https://music.apple.com/us/album/dreamboy/1892181271</v>
       </c>
       <c r="L138" t="str">
-        <v>Time to Time (Annie) - Daniel Seavey</v>
+        <v>DREAMBOY - MICO</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
+        <v>Time to Time (Annie)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
+        <v>https://music.apple.com/us/song/time-to-time-annie/1891399915</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
+        <v>Time to Time (Annie) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:23</v>
+        <v>2:52</v>
       </c>
       <c r="H139" t="str">
-        <v>The Two Lips</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
+        <v>https://music.apple.com/us/album/time-to-time-annie/1891399913</v>
       </c>
       <c r="L139" t="str">
-        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
+        <v>Time to Time (Annie) - Daniel Seavey</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>car crash</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
+        <v>https://music.apple.com/us/song/in-every-lifetime-from-the-prime-original-series-off-campus/1893969806</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>car crash - Single</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:40</v>
+        <v>3:23</v>
       </c>
       <c r="H140" t="str">
-        <v>jigitz</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
+        <v>https://music.apple.com/us/album/in-every-lifetime-from-the-prime-original-series-off-campus/1893969804</v>
       </c>
       <c r="L140" t="str">
-        <v>car crash - jigitz</v>
+        <v>In Every Lifetime (From the Prime Original Series, Off Campus) - The Two Lips</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>All This Disaster</v>
+        <v>car crash</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
+        <v>https://music.apple.com/us/song/car-crash/1888339561</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>All This Disaster - Single</v>
+        <v>car crash - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:22</v>
+        <v>2:40</v>
       </c>
       <c r="H141" t="str">
-        <v>Sarah McLachlan</v>
+        <v>jigitz</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
+        <v>https://music.apple.com/us/artist/jigitz/1212140410</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
+        <v>https://music.apple.com/us/album/car-crash/1888339560</v>
       </c>
       <c r="L141" t="str">
-        <v>All This Disaster - Sarah McLachlan</v>
+        <v>car crash - jigitz</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Better Days</v>
+        <v>All This Disaster</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/better-days/1893869499</v>
+        <v>https://music.apple.com/us/song/all-this-disaster/6761868750</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Let Love In (20th Anniversary Edition)</v>
+        <v>All This Disaster - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H142" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Sarah McLachlan</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sarah-mclachlan/111192</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/better-days/1893869157</v>
+        <v>https://music.apple.com/us/album/all-this-disaster/1891867887</v>
       </c>
       <c r="L142" t="str">
-        <v>Better Days - The Goo Goo Dolls</v>
+        <v>All This Disaster - Sarah McLachlan</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Rising Skyline</v>
+        <v>Better Days</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
+        <v>https://music.apple.com/us/song/better-days/1893869499</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Location Lost</v>
+        <v>Let Love In (20th Anniversary Edition)</v>
       </c>
       <c r="G143" t="str">
-        <v>4:32</v>
+        <v>3:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Failure</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
+        <v>https://music.apple.com/us/album/better-days/1893869157</v>
       </c>
       <c r="L143" t="str">
-        <v>The Rising Skyline - Failure</v>
+        <v>Better Days - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Cryogen</v>
+        <v>The Rising Skyline</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
+        <v>https://music.apple.com/us/song/the-rising-skyline/1867015669</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Wow! Signal</v>
+        <v>Location Lost</v>
       </c>
       <c r="G144" t="str">
-        <v>5:01</v>
+        <v>4:32</v>
       </c>
       <c r="H144" t="str">
-        <v>Muse</v>
+        <v>Failure</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
+        <v>https://music.apple.com/us/album/the-rising-skyline/1867015665</v>
       </c>
       <c r="L144" t="str">
-        <v>Cryogen - Muse</v>
+        <v>The Rising Skyline - Failure</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Harry Hole Theme</v>
+        <v>Cryogen</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
+        <v>https://music.apple.com/us/song/cryogen/1885607726</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G145" t="str">
-        <v>1:21</v>
+        <v>5:01</v>
       </c>
       <c r="H145" t="str">
-        <v>Nick Cave</v>
+        <v>Muse</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
+        <v>https://music.apple.com/us/album/cryogen/1885607338</v>
       </c>
       <c r="L145" t="str">
-        <v>Harry Hole Theme - Nick Cave</v>
+        <v>Cryogen - Muse</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>LIFE KEEPS GOING</v>
+        <v>Harry Hole Theme</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
+        <v>https://music.apple.com/us/song/harry-hole-theme/1893120500</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Jo Nesbø's Detective Hole (Original Series Soundtrack)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:39</v>
+        <v>1:21</v>
       </c>
       <c r="H146" t="str">
-        <v>Genesis Owusu</v>
+        <v>Nick Cave</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nick-cave/3691438</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
+        <v>https://music.apple.com/us/album/harry-hole-theme/1893120498</v>
       </c>
       <c r="L146" t="str">
-        <v>LIFE KEEPS GOING - Genesis Owusu</v>
+        <v>Harry Hole Theme - Nick Cave</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>HBO</v>
+        <v>LIFE KEEPS GOING</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/hbo/1886486458</v>
+        <v>https://music.apple.com/us/song/life-keeps-going/1887196758</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>HBO - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G147" t="str">
-        <v>3:42</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Yung Gravy</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/hbo/1886486453</v>
+        <v>https://music.apple.com/us/album/life-keeps-going/1887196431</v>
       </c>
       <c r="L147" t="str">
-        <v>HBO - Yung Gravy</v>
+        <v>LIFE KEEPS GOING - Genesis Owusu</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Need For Speed</v>
+        <v>HBO</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
+        <v>https://music.apple.com/us/song/hbo/1886486458</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Need For Speed - Single</v>
+        <v>HBO - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:15</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Kim Petras</v>
+        <v>Yung Gravy</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
+        <v>https://music.apple.com/us/artist/yung-gravy/1165036761</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
+        <v>https://music.apple.com/us/album/hbo/1886486453</v>
       </c>
       <c r="L148" t="str">
-        <v>Need For Speed - Kim Petras</v>
+        <v>HBO - Yung Gravy</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>collide</v>
+        <v>Need For Speed</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/collide/1893704561</v>
+        <v>https://music.apple.com/us/song/need-for-speed/1891480495</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>girls like girls (the album)</v>
+        <v>Need For Speed - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:43</v>
+        <v>3:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/kim-petras/291697579</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/collide/1893704396</v>
+        <v>https://music.apple.com/us/album/need-for-speed/1891480491</v>
       </c>
       <c r="L149" t="str">
-        <v>collide - Hayley Kiyoko</v>
+        <v>Need For Speed - Kim Petras</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>freak for you</v>
+        <v>collide</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
+        <v>https://music.apple.com/us/song/collide/1893704561</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>freak for you - Single</v>
+        <v>girls like girls (the album)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:26</v>
+        <v>3:43</v>
       </c>
       <c r="H150" t="str">
-        <v>Haiden Henderson</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
+        <v>https://music.apple.com/us/album/collide/1893704396</v>
       </c>
       <c r="L150" t="str">
-        <v>freak for you - Haiden Henderson</v>
+        <v>collide - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Anymore</v>
+        <v>freak for you</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/anymore/1893698894</v>
+        <v>https://music.apple.com/us/song/freak-for-you/1893848375</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Everything Is About You - Single</v>
+        <v>freak for you - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:26</v>
       </c>
       <c r="H151" t="str">
-        <v>Asha Banks</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/haiden-henderson/1553587317</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/anymore/1893698812</v>
+        <v>https://music.apple.com/us/album/freak-for-you/1893848369</v>
       </c>
       <c r="L151" t="str">
-        <v>Anymore - Asha Banks</v>
+        <v>freak for you - Haiden Henderson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Why Am I Here</v>
+        <v>Anymore</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
+        <v>https://music.apple.com/us/song/anymore/1893698894</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Sensitive to the room - EP</v>
+        <v>Everything Is About You - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:17</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Presley Regier</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
+        <v>https://music.apple.com/us/album/anymore/1893698812</v>
       </c>
       <c r="L152" t="str">
-        <v>Why Am I Here - Presley Regier</v>
+        <v>Anymore - Asha Banks</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>oh child</v>
+        <v>Why Am I Here</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
+        <v>https://music.apple.com/us/song/why-am-i-here/1888615780</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>oh child - Single</v>
+        <v>Sensitive to the room - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>2:02</v>
+        <v>3:17</v>
       </c>
       <c r="H153" t="str">
-        <v>kai devega</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
+        <v>https://music.apple.com/us/album/why-am-i-here/1888615442</v>
       </c>
       <c r="L153" t="str">
-        <v>oh child - kai devega</v>
+        <v>Why Am I Here - Presley Regier</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Leave Me For Good</v>
+        <v>oh child</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
+        <v>https://music.apple.com/us/song/oh-child/1894911539</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Leave Me For Good - Single</v>
+        <v>oh child - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:58</v>
+        <v>2:02</v>
       </c>
       <c r="H154" t="str">
-        <v>tbh</v>
+        <v>kai devega</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
+        <v>https://music.apple.com/us/album/oh-child/1894911537</v>
       </c>
       <c r="L154" t="str">
-        <v>Leave Me For Good - tbh</v>
+        <v>oh child - kai devega</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Dance To This</v>
+        <v>Leave Me For Good</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
+        <v>https://music.apple.com/us/song/leave-me-for-good/1891797747</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>Leave Me For Good - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>tbh</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/tbh/1861951760</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
+        <v>https://music.apple.com/us/album/leave-me-for-good/1891797746</v>
       </c>
       <c r="L155" t="str">
-        <v>Dance To This - Icona Pop</v>
+        <v>Leave Me For Good - tbh</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Breathe On It (Radio Version)</v>
+        <v>Dance To This</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
+        <v>https://music.apple.com/us/song/dance-to-this/1892426990</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Breathe On It (Radio Version) - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G156" t="str">
-        <v>3:58</v>
+        <v>2:54</v>
       </c>
       <c r="H156" t="str">
-        <v>Tauren Wells</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
+        <v>https://music.apple.com/us/album/dance-to-this/1892426976</v>
       </c>
       <c r="L156" t="str">
-        <v>Breathe On It (Radio Version) - Tauren Wells</v>
+        <v>Dance To This - Icona Pop</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You Can Have Him</v>
+        <v>Breathe On It (Radio Version)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
+        <v>https://music.apple.com/us/song/breathe-on-it-radio-version/1892432908</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You Can Have Him - Single</v>
+        <v>Breathe On It (Radio Version) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:15</v>
+        <v>3:58</v>
       </c>
       <c r="H157" t="str">
-        <v>Carly Pearce</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
+        <v>https://music.apple.com/us/album/breathe-on-it-radio-version/1892432906</v>
       </c>
       <c r="L157" t="str">
-        <v>You Can Have Him - Carly Pearce</v>
+        <v>Breathe On It (Radio Version) - Tauren Wells</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Backwards</v>
+        <v>You Can Have Him</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/backwards/1890336055</v>
+        <v>https://music.apple.com/us/song/you-can-have-him/1891361932</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Backwards - Single</v>
+        <v>You Can Have Him - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/backwards/1890336054</v>
+        <v>https://music.apple.com/us/album/you-can-have-him/1891361931</v>
       </c>
       <c r="L158" t="str">
-        <v>Backwards - Hudson Westbrook</v>
+        <v>You Can Have Him - Carly Pearce</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Love Ain't Shit</v>
+        <v>Backwards</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
+        <v>https://music.apple.com/us/song/backwards/1890336055</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Serial Romantic</v>
+        <v>Backwards - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H159" t="str">
-        <v>Jai'Len Josey</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
+        <v>https://music.apple.com/us/album/backwards/1890336054</v>
       </c>
       <c r="L159" t="str">
-        <v>Love Ain't Shit - Jai'Len Josey</v>
+        <v>Backwards - Hudson Westbrook</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>BACK IN MY ARMS</v>
+        <v>Love Ain't Shit</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
+        <v>https://music.apple.com/us/song/love-aint-shit/1892295190</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>BACK IN MY ARMS - Single</v>
+        <v>Serial Romantic</v>
       </c>
       <c r="G160" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Isaiah Falls</v>
+        <v>Jai'Len Josey</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
+        <v>https://music.apple.com/us/artist/jailen-josey/1496426886</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
+        <v>https://music.apple.com/us/album/love-aint-shit/1892294908</v>
       </c>
       <c r="L160" t="str">
-        <v>BACK IN MY ARMS - Isaiah Falls</v>
+        <v>Love Ain't Shit - Jai'Len Josey</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>2 NIGHTS IN LA</v>
+        <v>BACK IN MY ARMS</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
+        <v>https://music.apple.com/us/song/back-in-my-arms/1893442741</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>2 NIGHTS IN LA - Single</v>
+        <v>BACK IN MY ARMS - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:42</v>
+        <v>3:43</v>
       </c>
       <c r="H161" t="str">
-        <v>PARTYOF2</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
+        <v>https://music.apple.com/us/album/back-in-my-arms/1893442740</v>
       </c>
       <c r="L161" t="str">
-        <v>2 NIGHTS IN LA - PARTYOF2</v>
+        <v>BACK IN MY ARMS - Isaiah Falls</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dance In The USA</v>
+        <v>2 NIGHTS IN LA</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
+        <v>https://music.apple.com/us/song/2-nights-in-la/1892246760</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Dance In The USA - Single</v>
+        <v>2 NIGHTS IN LA - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:59</v>
+        <v>3:42</v>
       </c>
       <c r="H162" t="str">
-        <v>Show Me the Body</v>
+        <v>PARTYOF2</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/partyof2/1790556764</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
+        <v>https://music.apple.com/us/album/2-nights-in-la/1892246757</v>
       </c>
       <c r="L162" t="str">
-        <v>Dance In The USA - Show Me the Body</v>
+        <v>2 NIGHTS IN LA - PARTYOF2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Tremolo</v>
+        <v>Dance In The USA</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
+        <v>https://music.apple.com/us/song/dance-in-the-usa/1888229247</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Romanticize The Dive</v>
+        <v>Dance In The USA - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:43</v>
+        <v>2:59</v>
       </c>
       <c r="H163" t="str">
-        <v>Metric</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/metric/4125821</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
+        <v>https://music.apple.com/us/album/dance-in-the-usa/1888229242</v>
       </c>
       <c r="L163" t="str">
-        <v>Tremolo - Metric</v>
+        <v>Dance In The USA - Show Me the Body</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>In the Dark</v>
+        <v>Tremolo</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
+        <v>https://music.apple.com/us/song/tremolo/1861918614</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>The End is Not the End</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G164" t="str">
-        <v>3:52</v>
+        <v>3:43</v>
       </c>
       <c r="H164" t="str">
-        <v>Atreyu</v>
+        <v>Metric</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
+        <v>https://music.apple.com/us/album/tremolo/1861918507</v>
       </c>
       <c r="L164" t="str">
-        <v>In the Dark - Atreyu</v>
+        <v>Tremolo - Metric</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Picking Dragons’ Pockets</v>
+        <v>In the Dark</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
+        <v>https://music.apple.com/us/song/in-the-dark/1873286330</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G165" t="str">
-        <v>4:36</v>
+        <v>3:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Modest Mouse</v>
+        <v>Atreyu</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
+        <v>https://music.apple.com/us/album/in-the-dark/1873285466</v>
       </c>
       <c r="L165" t="str">
-        <v>Picking Dragons’ Pockets - Modest Mouse</v>
+        <v>In the Dark - Atreyu</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Saw Your Face</v>
+        <v>Picking Dragons’ Pockets</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
+        <v>https://music.apple.com/us/song/picking-dragons-pockets/1885992018</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Saw Your Face - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G166" t="str">
-        <v>3:09</v>
+        <v>4:36</v>
       </c>
       <c r="H166" t="str">
-        <v>Malcolm Todd</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
+        <v>https://music.apple.com/us/album/picking-dragons-pockets/1885991734</v>
       </c>
       <c r="L166" t="str">
-        <v>I Saw Your Face - Malcolm Todd</v>
+        <v>Picking Dragons’ Pockets - Modest Mouse</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Demons In Your Choir</v>
+        <v>I Saw Your Face</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
+        <v>https://music.apple.com/us/song/i-saw-your-face/6762312295</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Grateful</v>
+        <v>I Saw Your Face - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:16</v>
+        <v>3:09</v>
       </c>
       <c r="H167" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
+        <v>https://music.apple.com/us/album/i-saw-your-face/1893771800</v>
       </c>
       <c r="L167" t="str">
-        <v>Demons In Your Choir - The Red Clay Strays</v>
+        <v>I Saw Your Face - Malcolm Todd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Full Circle</v>
+        <v>Demons In Your Choir</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
+        <v>https://music.apple.com/us/song/demons-in-your-choir/1893402543</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>When You Turn Around - EP</v>
+        <v>Grateful</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Leonie Biney</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
+        <v>https://music.apple.com/us/album/demons-in-your-choir/1893402542</v>
       </c>
       <c r="L168" t="str">
-        <v>Full Circle - Leonie Biney</v>
+        <v>Demons In Your Choir - The Red Clay Strays</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Bitches Talk Shit</v>
+        <v>Full Circle</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
+        <v>https://music.apple.com/us/song/full-circle/1886704624</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Bitches Talk Shit - Single</v>
+        <v>When You Turn Around - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:39</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Sophia Stel</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
+        <v>https://music.apple.com/us/album/full-circle/1886704623</v>
       </c>
       <c r="L169" t="str">
-        <v>Bitches Talk Shit - Sophia Stel</v>
+        <v>Full Circle - Leonie Biney</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>No Trick (feat. Trim)</v>
+        <v>Bitches Talk Shit</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
+        <v>https://music.apple.com/us/song/bitches-talk-shit/1888034540</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Destined For Greatness</v>
+        <v>Bitches Talk Shit - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:03</v>
+        <v>3:39</v>
       </c>
       <c r="H170" t="str">
-        <v>Luh Tyler</v>
+        <v>Sophia Stel</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
+        <v>https://music.apple.com/us/artist/sophia-stel/1473708664</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
+        <v>https://music.apple.com/us/album/bitches-talk-shit/1888034538</v>
       </c>
       <c r="L170" t="str">
-        <v>No Trick (feat. Trim) - Luh Tyler</v>
+        <v>Bitches Talk Shit - Sophia Stel</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Motion (feat. G Herbo)</v>
+        <v>No Trick (feat. Trim)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
+        <v>https://music.apple.com/us/song/no-trick-feat-trim/6762713064</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sadetra Son</v>
+        <v>Destined For Greatness</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>2:03</v>
       </c>
       <c r="H171" t="str">
-        <v>Montana 700</v>
+        <v>Luh Tyler</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
+        <v>https://music.apple.com/us/artist/luh-tyler/1638445286</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
+        <v>https://music.apple.com/us/album/no-trick-feat-trim/1894977282</v>
       </c>
       <c r="L171" t="str">
-        <v>Motion (feat. G Herbo) - Montana 700</v>
+        <v>No Trick (feat. Trim) - Luh Tyler</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HIPSTER ENCORE</v>
+        <v>Motion (feat. G Herbo)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
+        <v>https://music.apple.com/us/song/motion-feat-g-herbo/1891854319</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>HIPSTER ENCORE - Single</v>
+        <v>Sadetra Son</v>
       </c>
       <c r="G172" t="str">
-        <v>2:31</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Thirteendegrees °</v>
+        <v>Montana 700</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
+        <v>https://music.apple.com/us/artist/montana-700/1619544692</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
+        <v>https://music.apple.com/us/album/motion-feat-g-herbo/1891854316</v>
       </c>
       <c r="L172" t="str">
-        <v>HIPSTER ENCORE - Thirteendegrees °</v>
+        <v>Motion (feat. G Herbo) - Montana 700</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ)</v>
+        <v>HIPSTER ENCORE</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
+        <v>https://music.apple.com/us/song/hipster-encore/1893778929</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
+        <v>HIPSTER ENCORE - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:28</v>
+        <v>2:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Beach Bunny</v>
+        <v>Thirteendegrees °</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
+        <v>https://music.apple.com/us/artist/thirteendegrees/1695191254</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
+        <v>https://music.apple.com/us/album/hipster-encore/1893778446</v>
       </c>
       <c r="L173" t="str">
-        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
+        <v>HIPSTER ENCORE - Thirteendegrees °</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Twice</v>
+        <v>Clueless (feat. Aly &amp; AJ)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/twice/1877978118</v>
+        <v>https://music.apple.com/us/song/clueless-feat-aly-aj/1891177212</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>I Think I've Heard This Before</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:32</v>
+        <v>3:28</v>
       </c>
       <c r="H174" t="str">
-        <v>Arrows in Action</v>
+        <v>Beach Bunny</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
+        <v>https://music.apple.com/us/artist/beach-bunny/1147783278</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/twice/1877978103</v>
+        <v>https://music.apple.com/us/album/clueless-feat-aly-aj/1891177196</v>
       </c>
       <c r="L174" t="str">
-        <v>Twice - Arrows in Action</v>
+        <v>Clueless (feat. Aly &amp; AJ) - Beach Bunny</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Asleep Talking</v>
+        <v>Twice</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
+        <v>https://music.apple.com/us/song/twice/1877978118</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Asleep Talking - Single</v>
+        <v>I Think I've Heard This Before</v>
       </c>
       <c r="G175" t="str">
-        <v>2:36</v>
+        <v>2:32</v>
       </c>
       <c r="H175" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Arrows in Action</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/arrows-in-action/1093697130</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
+        <v>https://music.apple.com/us/album/twice/1877978103</v>
       </c>
       <c r="L175" t="str">
-        <v>Asleep Talking - Magnus Ferrell</v>
+        <v>Twice - Arrows in Action</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>hide and seek</v>
+        <v>Asleep Talking</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
+        <v>https://music.apple.com/us/song/asleep-talking/1892157901</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>hide and seek - Single</v>
+        <v>Asleep Talking - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H176" t="str">
-        <v>Hailey Picardi</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
+        <v>https://music.apple.com/us/album/asleep-talking/1892157897</v>
       </c>
       <c r="L176" t="str">
-        <v>hide and seek - Hailey Picardi</v>
+        <v>Asleep Talking - Magnus Ferrell</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Be the One</v>
+        <v>hide and seek</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
+        <v>https://music.apple.com/us/song/hide-and-seek/6762668748</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Be the One - Single</v>
+        <v>hide and seek - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:25</v>
+        <v>2:47</v>
       </c>
       <c r="H177" t="str">
-        <v>Adam Port</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
+        <v>https://music.apple.com/us/album/hide-and-seek/1894953064</v>
       </c>
       <c r="L177" t="str">
-        <v>Be the One - Adam Port</v>
+        <v>hide and seek - Hailey Picardi</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
+        <v>https://music.apple.com/us/song/be-the-one/1889517558</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>World Is Mine</v>
+        <v>Be the One - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:46</v>
+        <v>3:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Lane 8</v>
+        <v>Adam Port</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/adam-port/314014291</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
+        <v>https://music.apple.com/us/album/be-the-one/1889517554</v>
       </c>
       <c r="L178" t="str">
-        <v>World Is Mine - Lane 8</v>
+        <v>Be the One - Adam Port</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Invite</v>
+        <v>World Is Mine</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
+        <v>https://music.apple.com/us/song/world-is-mine/1887298647</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>The Last Balloon</v>
+        <v>World Is Mine</v>
       </c>
       <c r="G179" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Lane 8</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
+        <v>https://music.apple.com/us/album/world-is-mine/1887298645</v>
       </c>
       <c r="L179" t="str">
-        <v>No Invite - Tank and the Bangas</v>
+        <v>World Is Mine - Lane 8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Bando</v>
+        <v>No Invite</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/bando/1880707634</v>
+        <v>https://music.apple.com/us/song/no-invite/1882831454</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HOPE!!</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Angélique Kidjo</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/bando/1880707227</v>
+        <v>https://music.apple.com/us/album/no-invite/1882831446</v>
       </c>
       <c r="L180" t="str">
-        <v>Bando - Angélique Kidjo</v>
+        <v>No Invite - Tank and the Bangas</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Misdemeanour (Feat. Låpsley)</v>
+        <v>Bando</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
+        <v>https://music.apple.com/us/song/bando/1880707634</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Single</v>
+        <v>HOPE!!</v>
       </c>
       <c r="G181" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>Duke Dumont</v>
+        <v>Angélique Kidjo</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A9lique-kidjo/468296</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
+        <v>https://music.apple.com/us/album/bando/1880707227</v>
       </c>
       <c r="L181" t="str">
-        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
+        <v>Bando - Angélique Kidjo</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Physical</v>
+        <v>Misdemeanour (Feat. Låpsley)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/physical/1891816798</v>
+        <v>https://music.apple.com/us/song/misdemeanour-feat-l%C3%A5psley/1888442878</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Physical - Single</v>
+        <v>Misdemeanour (Feat. Låpsley) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>2:31</v>
       </c>
       <c r="H182" t="str">
-        <v>J. Worra</v>
+        <v>Duke Dumont</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
+        <v>https://music.apple.com/us/artist/duke-dumont/257148267</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/physical/1891816796</v>
+        <v>https://music.apple.com/us/album/misdemeanour-feat-l%C3%A5psley/1888442876</v>
       </c>
       <c r="L182" t="str">
-        <v>Physical - J. Worra</v>
+        <v>Misdemeanour (Feat. Låpsley) - Duke Dumont</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP</v>
+        <v>Physical</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
+        <v>https://music.apple.com/us/song/physical/1891816798</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H183" t="str">
-        <v>LEGADO 7</v>
+        <v>J. Worra</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/j-worra/964744411</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
+        <v>https://music.apple.com/us/album/physical/1891816796</v>
       </c>
       <c r="L183" t="str">
-        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
+        <v>Physical - J. Worra</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>AM I OKAY?!</v>
+        <v>LOS MENSAJES DE WHATSAPP</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
+        <v>https://music.apple.com/us/song/los-mensajes-de-whatsapp/1893167657</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>AM I OKAY?! - Single</v>
+        <v>LOS MENSAJES DE WHATSAPP - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H184" t="str">
-        <v>Durand Bernarr</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
+        <v>https://music.apple.com/us/album/los-mensajes-de-whatsapp/1893167641</v>
       </c>
       <c r="L184" t="str">
-        <v>AM I OKAY?! - Durand Bernarr</v>
+        <v>LOS MENSAJES DE WHATSAPP - LEGADO 7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Have You Ever</v>
+        <v>AM I OKAY?!</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
+        <v>https://music.apple.com/us/song/am-i-okay/1893426050</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Have You Ever - Single</v>
+        <v>AM I OKAY?! - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:04</v>
+        <v>3:37</v>
       </c>
       <c r="H185" t="str">
-        <v>FEYI</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/feyi/268786779</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
+        <v>https://music.apple.com/us/album/am-i-okay/1893426049</v>
       </c>
       <c r="L185" t="str">
-        <v>Have You Ever - FEYI</v>
+        <v>AM I OKAY?! - Durand Bernarr</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Campeones</v>
+        <v>Have You Ever</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/campeones/1884690458</v>
+        <v>https://music.apple.com/us/song/have-you-ever/1892015053</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Campeones - Single</v>
+        <v>Have You Ever - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H186" t="str">
-        <v>Cypress Hill</v>
+        <v>FEYI</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
+        <v>https://music.apple.com/us/artist/feyi/268786779</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/campeones/1884690456</v>
+        <v>https://music.apple.com/us/album/have-you-ever/1892015050</v>
       </c>
       <c r="L186" t="str">
-        <v>Campeones - Cypress Hill</v>
+        <v>Have You Ever - FEYI</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>My Light (feat. Sufjan Stevens)</v>
+        <v>Campeones</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
+        <v>https://music.apple.com/us/song/campeones/1884690458</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Compass Rosa (Expanded Version)</v>
+        <v>Campeones - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:27</v>
+        <v>3:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Mina Tindle</v>
+        <v>Cypress Hill</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
+        <v>https://music.apple.com/us/artist/cypress-hill/465802</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
+        <v>https://music.apple.com/us/album/campeones/1884690456</v>
       </c>
       <c r="L187" t="str">
-        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
+        <v>Campeones - Cypress Hill</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>tennis practice</v>
+        <v>My Light (feat. Sufjan Stevens)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
+        <v>https://music.apple.com/us/song/my-light-feat-sufjan-stevens/1886118516</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>exposure therapy - EP</v>
+        <v>Compass Rosa (Expanded Version)</v>
       </c>
       <c r="G188" t="str">
-        <v>2:41</v>
+        <v>3:27</v>
       </c>
       <c r="H188" t="str">
-        <v>Khatumu</v>
+        <v>Mina Tindle</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
+        <v>https://music.apple.com/us/artist/mina-tindle/317799614</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
+        <v>https://music.apple.com/us/album/my-light-feat-sufjan-stevens/1886118345</v>
       </c>
       <c r="L188" t="str">
-        <v>tennis practice - Khatumu</v>
+        <v>My Light (feat. Sufjan Stevens) - Mina Tindle</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Moon Not Mine</v>
+        <v>tennis practice</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
+        <v>https://music.apple.com/us/song/tennis-practice/1874037659</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Singing</v>
+        <v>exposure therapy - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Gia Margaret</v>
+        <v>Khatumu</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/khatumu/1662571415</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
+        <v>https://music.apple.com/us/album/tennis-practice/1874037279</v>
       </c>
       <c r="L189" t="str">
-        <v>Moon Not Mine - Gia Margaret</v>
+        <v>tennis practice - Khatumu</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>You Say I Love You</v>
+        <v>Moon Not Mine</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
+        <v>https://music.apple.com/us/song/moon-not-mine/1869047394</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Blue Angel Sparkling Silver 2</v>
+        <v>Singing</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H190" t="str">
-        <v>Quiet Light</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
+        <v>https://music.apple.com/us/album/moon-not-mine/1869047383</v>
       </c>
       <c r="L190" t="str">
-        <v>You Say I Love You - Quiet Light</v>
+        <v>Moon Not Mine - Gia Margaret</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>You Say I Love You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
+        <v>https://music.apple.com/us/song/you-say-i-love-you/1868660549</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Something Worth Waiting For</v>
+        <v>Blue Angel Sparkling Silver 2</v>
       </c>
       <c r="G191" t="str">
-        <v>5:54</v>
+        <v>3:06</v>
       </c>
       <c r="H191" t="str">
-        <v>Friko</v>
+        <v>Quiet Light</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/friko/1488035324</v>
+        <v>https://music.apple.com/us/artist/quiet-light/1504830947</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
+        <v>https://music.apple.com/us/album/you-say-i-love-you/1868660166</v>
       </c>
       <c r="L191" t="str">
-        <v>Something Worth Waiting For - Friko</v>
+        <v>You Say I Love You - Quiet Light</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Guqa (My Prayer)</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
+        <v>https://music.apple.com/us/song/something-worth-waiting-for/1866639062</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Izinja Zam: Vol. I - EP</v>
+        <v>Something Worth Waiting For</v>
       </c>
       <c r="G192" t="str">
-        <v>7:05</v>
+        <v>5:54</v>
       </c>
       <c r="H192" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Friko</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/friko/1488035324</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
+        <v>https://music.apple.com/us/album/something-worth-waiting-for/1866639054</v>
       </c>
       <c r="L192" t="str">
-        <v>Guqa (My Prayer) - Zee Nxumalo</v>
+        <v>Something Worth Waiting For - Friko</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Cake</v>
+        <v>Guqa (My Prayer)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/cake/1888461230</v>
+        <v>https://music.apple.com/us/song/guqa-my-prayer/1892100621</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cake - Single</v>
+        <v>Izinja Zam: Vol. I - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>2:36</v>
+        <v>7:05</v>
       </c>
       <c r="H193" t="str">
-        <v>Mila Smith</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/cake/1888461226</v>
+        <v>https://music.apple.com/us/album/guqa-my-prayer/1892100618</v>
       </c>
       <c r="L193" t="str">
-        <v>Cake - Mila Smith</v>
+        <v>Guqa (My Prayer) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>from a distance</v>
+        <v>Cake</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
+        <v>https://music.apple.com/us/song/cake/1888461230</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>from a distance - Single</v>
+        <v>Cake - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H194" t="str">
-        <v>Luz</v>
+        <v>Mila Smith</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/luz/1112766739</v>
+        <v>https://music.apple.com/us/artist/mila-smith/1450040784</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
+        <v>https://music.apple.com/us/album/cake/1888461226</v>
       </c>
       <c r="L194" t="str">
-        <v>from a distance - Luz</v>
+        <v>Cake - Mila Smith</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Second Hand</v>
+        <v>from a distance</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
+        <v>https://music.apple.com/us/song/from-a-distance/1888508569</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Second Hand - Single</v>
+        <v>from a distance - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Luz</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/luz/1112766739</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
+        <v>https://music.apple.com/us/album/from-a-distance/1888508568</v>
       </c>
       <c r="L195" t="str">
-        <v>Second Hand - Anais Cardot</v>
+        <v>from a distance - Luz</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mnikeni</v>
+        <v>Second Hand</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
+        <v>https://music.apple.com/us/song/second-hand/1882333935</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Ku Ngawe</v>
+        <v>Second Hand - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H196" t="str">
-        <v>Thando Zide</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
+        <v>https://music.apple.com/us/album/second-hand/1882333934</v>
       </c>
       <c r="L196" t="str">
-        <v>Mnikeni - Thando Zide</v>
+        <v>Second Hand - Anais Cardot</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Lorcan's Song</v>
+        <v>Mnikeni</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
+        <v>https://music.apple.com/us/song/mnikeni/6762762642</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
+        <v>Ku Ngawe</v>
       </c>
       <c r="G197" t="str">
-        <v>2:40</v>
+        <v>3:08</v>
       </c>
       <c r="H197" t="str">
-        <v>Christian Henson</v>
+        <v>Thando Zide</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
+        <v>https://music.apple.com/us/artist/thando-zide/1593457857</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
+        <v>https://music.apple.com/us/album/mnikeni/1894999794</v>
       </c>
       <c r="L197" t="str">
-        <v>Lorcan's Song - Christian Henson</v>
+        <v>Mnikeni - Thando Zide</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>In Dark Distortion</v>
+        <v>Lorcan's Song</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
+        <v>https://music.apple.com/us/song/lorcans-song/1891140334</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-30</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>My Brother The Minotaur (Apple Original Series Soundtrack)</v>
       </c>
       <c r="G198" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H198" t="str">
-        <v>At The Gates</v>
+        <v>Christian Henson</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/christian-henson/73071590</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
+        <v>https://music.apple.com/us/album/lorcans-song/1891140330</v>
       </c>
       <c r="L198" t="str">
-        <v>In Dark Distortion - At The Gates</v>
+        <v>Lorcan's Song - Christian Henson</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>All Souls Rising</v>
+        <v>In Dark Distortion</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
+        <v>https://music.apple.com/us/song/in-dark-distortion/1873364817</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-30</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G199" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H199" t="str">
-        <v>Sepultura</v>
+        <v>At The Gates</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
+        <v>https://music.apple.com/us/album/in-dark-distortion/1873364809</v>
       </c>
       <c r="L199" t="str">
-        <v>All Souls Rising - Sepultura</v>
+        <v>In Dark Distortion - At The Gates</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Other Hells</v>
+        <v>All Souls Rising</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+        <v>https://music.apple.com/us/song/all-souls-rising/1869119579</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-30</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Other Hells - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G200" t="str">
-        <v>2:06</v>
+        <v>3:35</v>
       </c>
       <c r="H200" t="str">
-        <v>Ceremony</v>
+        <v>Sepultura</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+        <v>https://music.apple.com/us/album/all-souls-rising/1869119453</v>
       </c>
       <c r="L200" t="str">
-        <v>Other Hells - Ceremony</v>
+        <v>All Souls Rising - Sepultura</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Other Hells</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/other-hells/1889890565</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Other Hells - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:06</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Ceremony</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/ceremony/157791080</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/other-hells/1889890562</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Other Hells - Ceremony</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Hit a Moonshot</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/hit-a-moonshot/1872193864</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-30</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>4:34</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/hit-a-moonshot/1872193859</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Hit a Moonshot - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week05/titles.xlsx
+++ b/data/global/2026-04-week05/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
